--- a/AAII_Financials/Quarterly/FOSL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FOSL_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
   <si>
     <t>FOSL</t>
   </si>
@@ -656,408 +656,420 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45108</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45017</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44835</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44744</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44653</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44562</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44471</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44380</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44289</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44198</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44107</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44016</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43925</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43827</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43736</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43645</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43554</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43463</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43372</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43099</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42917</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42826</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>421300</v>
+      </c>
+      <c r="E8" s="3">
         <v>344100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>322000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>325000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>499100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>436300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>371200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>375900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>604200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>491800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>410900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>363000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>528100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>435500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>259000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>390700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>711600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>539500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>501400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>465300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>786900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>608800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>576600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>569200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>920800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>688700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>596800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>581800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>959200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>738000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>222000</v>
+      </c>
+      <c r="E9" s="3">
         <v>183800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>162400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>159100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>263800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>216700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>179800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>191500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>301800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>232300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>189100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>180500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>268500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>205700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>118400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>250400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>403700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>260900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>236300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>217300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>370000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>282300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>267600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>281500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>472700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>368800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>295500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>292300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>470100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>352900</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>199300</v>
+      </c>
+      <c r="E10" s="3">
         <v>160300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>159600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>165900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>235400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>219600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>191400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>184400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>302400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>259500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>221800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>182500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>259600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>229800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>140600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>140300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>307900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>278600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>265100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>248000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>416900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>326500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>309000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>287700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>448100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>319900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>301300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>289500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>489100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>385100</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1090,8 +1102,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1182,8 +1195,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1274,100 +1290,106 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E14" s="3">
         <v>15300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>7700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>12400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>6100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>6000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>7000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>12000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>17800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>9700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>14100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>28600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>12800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>25100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>9000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>11000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>4800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>6200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>21000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>23500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>6400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>5800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>416900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>26300</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>13300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1395,8 +1417,8 @@
       <c r="K15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L15" s="3">
-        <v>100</v>
+      <c r="L15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M15" s="3">
         <v>100</v>
@@ -1426,10 +1448,10 @@
         <v>100</v>
       </c>
       <c r="V15" s="3">
+        <v>100</v>
+      </c>
+      <c r="W15" s="3">
         <v>400</v>
-      </c>
-      <c r="W15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>8</v>
@@ -1440,8 +1462,8 @@
       <c r="Z15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA15" s="3">
-        <v>0</v>
+      <c r="AA15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB15" s="3">
         <v>0</v>
@@ -1458,8 +1480,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1489,192 +1514,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>445300</v>
+      </c>
+      <c r="E17" s="3">
         <v>390500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>357300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>362300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>497900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>413800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>382100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>390100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>557000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>444000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>396600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>379800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>509800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>418000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>295800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>525100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>715600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>548600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>499700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>485200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>719600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>586200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>575600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>598100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>869600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>689200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1026600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>627100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>893000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>706800</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-46400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-35300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-37300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>22500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-10900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-14200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>47200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>47800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>14300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-16800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>18300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>17500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-36800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-134400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-4000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-9100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-19900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>67300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>22600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-28900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>51200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-429800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-45300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>66200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>31200</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1707,468 +1739,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>7100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-15400</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-500</v>
       </c>
       <c r="M20" s="3">
         <v>-500</v>
       </c>
       <c r="N20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="O20" s="3">
         <v>1900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1600</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-7300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>5000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>25900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>5300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>3900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>5600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>7600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-44900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-23300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-29500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>7500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>26300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-6800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-6500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>38100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>54300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>21300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-6000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>29900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>27800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-25200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-129400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>14000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>16100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>20400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>93100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>35800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>15500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-14200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>72900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>22800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-406600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-18700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>95200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>56300</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E22" s="3">
         <v>5800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>5300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>5800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>5100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>4300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>4000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>4800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>6400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>6500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>7300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>8500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>8000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>7900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>7500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>7000</v>
-      </c>
-      <c r="T22" s="3">
-        <v>7400</v>
       </c>
       <c r="U22" s="3">
         <v>7400</v>
       </c>
       <c r="V22" s="3">
+        <v>7400</v>
+      </c>
+      <c r="W22" s="3">
         <v>8100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>10800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>9900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>11100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>10700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>11100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>12100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>11600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>8400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>7500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>7000</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-55200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-33500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-39600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>15500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-16900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-16700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>27100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>40900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-22200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>11400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>9500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-43800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-149100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-18000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>61800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>9900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-10600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-40900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>42400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-8700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-439400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-48000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>66300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>25800</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>600</v>
+      </c>
+      <c r="E24" s="3">
         <v>5600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-7200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>9200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>9000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>8100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>15200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-20800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-63700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>6900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>9600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>13900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>6600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>87000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-96300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>15500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2259,192 +2307,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-28400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-60800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-26300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-41200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-18900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-21300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>19800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>31900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-24300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>16200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-23000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-85400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-6700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-24900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-6600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-11800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>47900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>5900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-7200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-47500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-44600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-5500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-343100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-46800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>50800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-61100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-26500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-41300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-9400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-19100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-21500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>19600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>31400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-24400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>16000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-22500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-85600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-6900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-25900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-7300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-12200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>47600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-7800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-48300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-46300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-5400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-344700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-48200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>49700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2535,8 +2592,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2591,8 +2651,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -2609,11 +2669,11 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-33600</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2627,8 +2687,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2719,8 +2782,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2811,192 +2877,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E32" s="3">
         <v>3100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-7100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>15400</v>
-      </c>
-      <c r="L32" s="3">
-        <v>500</v>
       </c>
       <c r="M32" s="3">
         <v>500</v>
       </c>
       <c r="N32" s="3">
+        <v>500</v>
+      </c>
+      <c r="O32" s="3">
         <v>-1900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1600</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>7300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-5000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-25900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-5300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-5600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-7600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-61100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-26500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-41300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-19100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-21500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>19600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>31400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-24400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>16000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-22500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-85600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-6900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-25900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-7300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-12200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>47600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-7800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-48300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-79900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-5400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-344700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-48200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>49700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3087,197 +3162,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-61100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-26500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-41300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-19100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-21500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>19600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>31400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-24400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>16000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-22500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-85600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-6900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-25900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-7300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-12200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>47600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-7800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-48300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-79900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-5400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-344700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-48200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>49700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45108</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45017</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44835</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44744</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44653</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44562</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44471</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44380</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44289</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44198</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44107</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44016</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43925</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43827</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43736</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43645</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43554</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43463</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43372</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43099</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42917</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42826</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3310,8 +3394,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3344,100 +3429,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>117200</v>
+      </c>
+      <c r="E41" s="3">
         <v>116100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>132100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>127100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>198700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>162600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>167100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>162600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>250800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>181800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>252300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>246700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>316000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>323600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>277600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>245400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>200200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>147500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>226600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>271400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>403400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>236100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>241800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>229900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>231200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>166900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>319800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>320700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>297300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>236000</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3528,376 +3617,391 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>187900</v>
+      </c>
+      <c r="E43" s="3">
         <v>194000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>162700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>168900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>206100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>215000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>176500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>201100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>255100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>251500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>187600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>175500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>229800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>189800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>130100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>153400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>289700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>247600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>204200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>199900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>328000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>261700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>204700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>234200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>367000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>310900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>240400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>245300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>375500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>321300</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>252800</v>
+      </c>
+      <c r="E44" s="3">
         <v>326700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>323900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>336500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>376000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>452700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>437900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>385800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>346900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>398300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>352000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>322500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>295300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>359500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>375900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>439700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>452300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>570300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>460300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>384100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>377600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>521300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>497800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>530700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>573800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>683000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>618100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>571500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>542500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>699600</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>152700</v>
+      </c>
+      <c r="E45" s="3">
         <v>148100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>178800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>171900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>164400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>185000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>183300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>187700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>169900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>155800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>157300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>202400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>149400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>134900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>98100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>128600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>117200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>126400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>124400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>133100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>149600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>129400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>125000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>161700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>118900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>125500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>126500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>142800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>132000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>132700</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>710700</v>
+      </c>
+      <c r="E46" s="3">
         <v>784900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>797600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>804500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>945300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1015300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>964800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>937200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1022800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>987500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>949200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>947100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>990500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1007800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>881700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>967100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1059500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1091700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1015500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>988500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1258600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1148500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1069300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1156400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1291000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1286300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1304800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1280300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1347300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1389600</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3913,47 +4017,47 @@
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="3">
-        <v>300</v>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I47" s="3">
         <v>300</v>
       </c>
       <c r="J47" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K47" s="3">
         <v>400</v>
       </c>
       <c r="L47" s="3">
+        <v>400</v>
+      </c>
+      <c r="M47" s="3">
         <v>5400</v>
-      </c>
-      <c r="M47" s="3">
-        <v>6800</v>
       </c>
       <c r="N47" s="3">
         <v>6800</v>
       </c>
       <c r="O47" s="3">
+        <v>6800</v>
+      </c>
+      <c r="P47" s="3">
         <v>59100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>58000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>90400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>67000</v>
-      </c>
-      <c r="S47" s="3">
-        <v>7000</v>
       </c>
       <c r="T47" s="3">
         <v>7000</v>
       </c>
       <c r="U47" s="3">
-        <v>7600</v>
+        <v>7000</v>
       </c>
       <c r="V47" s="3">
         <v>7600</v>
@@ -3962,7 +4066,7 @@
         <v>7600</v>
       </c>
       <c r="X47" s="3">
-        <v>1000</v>
+        <v>7600</v>
       </c>
       <c r="Y47" s="3">
         <v>1000</v>
@@ -3974,13 +4078,13 @@
         <v>1000</v>
       </c>
       <c r="AB47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AC47" s="3">
         <v>900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>7400</v>
-      </c>
-      <c r="AD47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE47" s="3" t="s">
         <v>8</v>
@@ -3988,192 +4092,201 @@
       <c r="AF47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>208200</v>
+      </c>
+      <c r="E48" s="3">
         <v>223100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>220800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>225700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>236800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>233800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>249200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>251800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>267400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>280700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>297100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>316800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>340800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>363000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>387200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>407800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>439700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>447100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>470600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>484700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>183200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>190600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>200100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>208500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>219700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>243400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>255800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>260400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>273900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>290800</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11400</v>
+      </c>
+      <c r="E49" s="3">
         <v>11600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>13600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>15000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>15800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>16500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>17800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>19300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>20800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>22400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>26900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>28000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>46400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>48100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>68300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>71300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>74300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>83900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>86700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>89500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>92500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>499800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>502400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>515800</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4264,8 +4377,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4356,100 +4472,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>47700</v>
+      </c>
+      <c r="E52" s="3">
         <v>43700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>43300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>44000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>44100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>53100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>56100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>62300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>63900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>67400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>68600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>61900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>70400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>74300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>71300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>68200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>71700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>66800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>68100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>61100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>57600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>58100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>61600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>65900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>59900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>130100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>115500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>61100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>63400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>61500</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4540,100 +4662,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>978000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1063200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1073400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1086000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1238100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1315000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1283400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1265300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1368700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1356000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1337400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1349100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1478500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1522300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1451300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1532600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1604700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1640600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1608200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1589900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1575200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1469500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1406200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1515700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1658400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1750400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1776000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2101700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2186900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2257600</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4666,8 +4794,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4700,100 +4829,104 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>147200</v>
+      </c>
+      <c r="E57" s="3">
         <v>158000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>139800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>120100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>191100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>204000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>208700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>198500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>229900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>246300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>213500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>201200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>178200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>213100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>127900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>132700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>172200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>193000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>178500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>138300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>169600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>159400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>139500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>133700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>205000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>248800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>163500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>151200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>163600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>193600</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4801,19 +4934,19 @@
         <v>500</v>
       </c>
       <c r="E58" s="3">
+        <v>500</v>
+      </c>
+      <c r="F58" s="3">
         <v>400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>400</v>
-      </c>
-      <c r="I58" s="3">
-        <v>600</v>
       </c>
       <c r="J58" s="3">
         <v>600</v>
@@ -4822,61 +4955,61 @@
         <v>600</v>
       </c>
       <c r="L58" s="3">
+        <v>600</v>
+      </c>
+      <c r="M58" s="3">
         <v>41200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>38400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>37900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>41600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>21400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>25200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>21100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>26200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>21900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>66400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>65900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>126400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>128000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>127700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>127100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>40200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>32700</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>26400</v>
       </c>
       <c r="AE58" s="3">
         <v>26400</v>
@@ -4884,376 +5017,391 @@
       <c r="AF58" s="3">
         <v>26400</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>26400</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>194800</v>
+      </c>
+      <c r="E59" s="3">
         <v>190100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>181200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>184600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>234400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>224300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>212000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>233500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>305200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>281900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>269900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>268100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>338800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>315400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>310600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>309400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>360800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>314300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>282700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>292400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>309800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>283800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>240300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>263100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>302000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>264500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>217800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>209100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>224600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>204200</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>342500</v>
+      </c>
+      <c r="E60" s="3">
         <v>348600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>321500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>305100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>425900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>428700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>421300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>432700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>535600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>569400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>521800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>507200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>558500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>549900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>463700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>463200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>559200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>529100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>527600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>496500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>605800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>571200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>507500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>523900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>509100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>553500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>414100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>386700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>414600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>424100</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>207000</v>
+      </c>
+      <c r="E61" s="3">
         <v>255900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>243000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>234600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>216100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>293600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>248900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>183900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>141400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>97400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>139700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>157200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>185900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>217900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>243900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>298500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>178800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>242100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>162000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>161100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>269800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>269100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>268400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>335500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>443900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>444300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>613600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>589700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>610000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>697400</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>176800</v>
+      </c>
+      <c r="E62" s="3">
         <v>180000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>171900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>180000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>193100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>202400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>219200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>219300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>226400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>246300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>266600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>275800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>294100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>331000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>347100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>354500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>362900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>359500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>379000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>383000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>111000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>99600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>113500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>129700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>124400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>99600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>93500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>142900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>146900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>151100</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5344,8 +5492,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5436,8 +5587,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5528,100 +5682,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>723800</v>
+      </c>
+      <c r="E66" s="3">
         <v>782100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>733900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>716900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>832200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>921900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>886200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>838200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>905500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>915000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>929600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>941300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1039400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1099500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1055300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1117100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1101700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1131400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1069000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1044200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>989700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>942700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>891200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>994200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1082200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1109100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1132900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1129800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1180700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1284900</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5654,8 +5814,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5746,8 +5907,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5838,8 +6002,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5930,8 +6097,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6022,100 +6192,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E72" s="3">
         <v>46600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>107700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>134200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>175500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>184900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>179100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>198100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>229100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>209500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>178100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>179300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>203700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>207700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>191700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>214200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>299800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>306700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>332600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>339900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>381600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>332000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>327000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>334800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>409700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>489500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>494900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>839600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>887800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>838100</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6206,8 +6382,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6298,8 +6477,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6390,100 +6572,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>254200</v>
+      </c>
+      <c r="E76" s="3">
         <v>281100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>339500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>369100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>405900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>393000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>397300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>427200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>463200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>440900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>407900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>407800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>439100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>422800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>396100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>415400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>503100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>509300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>539200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>545700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>585500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>526800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>515000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>521400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>576100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>641300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>643000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>971900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1006200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>972700</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6574,197 +6762,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45108</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45017</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44835</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44744</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44653</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44562</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44471</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44380</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44289</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44198</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44107</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44016</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43925</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43827</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43736</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43645</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43554</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43463</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43372</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43099</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42917</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42826</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-61100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-26500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-41300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-19100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-21500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>19600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>31400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-24400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>16000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-22500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-85600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-6900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-25900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-7300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-12200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>47600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-7800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-48300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-79900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-5400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-344700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-48200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>49700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6797,8 +6994,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6806,91 +7004,94 @@
         <v>4600</v>
       </c>
       <c r="E83" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F83" s="3">
         <v>4800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5800</v>
-      </c>
-      <c r="J83" s="3">
-        <v>6200</v>
       </c>
       <c r="K83" s="3">
         <v>6200</v>
       </c>
       <c r="L83" s="3">
+        <v>6200</v>
+      </c>
+      <c r="M83" s="3">
         <v>7000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>8900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>10000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>10300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>10700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>12200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>12900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>13500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>13900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>14400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>20400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>16100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>15100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>16000</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>19400</v>
       </c>
       <c r="AB83" s="3">
         <v>19400</v>
       </c>
       <c r="AC83" s="3">
+        <v>19400</v>
+      </c>
+      <c r="AD83" s="3">
         <v>21200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>20900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>21400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6981,8 +7182,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7073,8 +7277,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7165,8 +7372,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7257,8 +7467,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7349,100 +7562,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>48500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-24900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-85900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>103900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-49000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-50700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-115000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>87000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-27200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>28100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-37800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>84200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>88800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-77100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>124000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-112100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-33700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>7600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>175700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-4900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>81700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>119400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>24800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-16000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>51400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>150800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-12600</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7475,100 +7694,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-6800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-6600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-7800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-8300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-8400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-8800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-12200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-14200</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7659,8 +7882,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7751,100 +7977,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>15100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-7600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>35300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-8500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-7800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-4300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-7500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>30100</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7877,8 +8109,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7969,8 +8202,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8061,8 +8297,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8153,8 +8392,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8245,280 +8487,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-49400</v>
+      </c>
+      <c r="E100" s="3">
         <v>12500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>16500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-79200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>44000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>56100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>32100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-15100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-41200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-22100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-34200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-14900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-32900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-53700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>112300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-66300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>36300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-6100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-172400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-71700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>12000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-45200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-162900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>28500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-22000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-92600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-12300</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>6600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>3200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1300</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>1000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-6600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>4100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>12500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>600</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>-2300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>4800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>3500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>4700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-10600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>10800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-16200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-71800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>30400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-88800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>68800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-71300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-63500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>46400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>32500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>44500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>52700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-79400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-44600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-131800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>173100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-5800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>11900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>64300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-152900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>23500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>61400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>4100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FOSL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FOSL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>FOSL</t>
   </si>
@@ -656,420 +656,433 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E7" s="2">
         <v>45290</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45108</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45017</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44835</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44744</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44653</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44562</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44471</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44380</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44289</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44198</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44107</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44016</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43925</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43827</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43736</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43645</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43554</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43463</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43372</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43099</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42917</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42826</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>254900</v>
+      </c>
+      <c r="E8" s="3">
         <v>421300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>344100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>322000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>325000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>499100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>436300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>371200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>375900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>604200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>491800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>410900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>363000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>528100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>435500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>259000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>390700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>711600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>539500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>501400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>465300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>786900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>608800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>576600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>569200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>920800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>688700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>596800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>581800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>959200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>738000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>121600</v>
+      </c>
+      <c r="E9" s="3">
         <v>222000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>183800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>162400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>159100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>263800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>216700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>179800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>191500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>301800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>232300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>189100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>180500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>268500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>205700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>118400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>250400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>403700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>260900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>236300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>217300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>370000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>282300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>267600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>281500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>472700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>368800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>295500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>292300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>470100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>352900</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>133300</v>
+      </c>
+      <c r="E10" s="3">
         <v>199300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>160300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>159600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>165900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>235400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>219600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>191400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>184400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>302400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>259500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>221800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>182500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>259600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>229800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>140600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>140300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>307900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>278600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>265100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>248000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>416900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>326500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>309000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>287700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>448100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>319900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>301300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>289500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>489100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>385100</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1103,8 +1116,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1198,8 +1212,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1293,103 +1310,109 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E14" s="3">
         <v>15600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>15300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>7700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>12400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>6100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>6000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>7000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>12000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>17800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>9700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>14100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>28600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>12800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>25100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>9000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>11000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>4800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>6200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>21000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>23500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>6400</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>5800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>416900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>26300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>13300</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1420,8 +1443,8 @@
       <c r="L15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M15" s="3">
-        <v>100</v>
+      <c r="M15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N15" s="3">
         <v>100</v>
@@ -1451,10 +1474,10 @@
         <v>100</v>
       </c>
       <c r="W15" s="3">
+        <v>100</v>
+      </c>
+      <c r="X15" s="3">
         <v>400</v>
-      </c>
-      <c r="X15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y15" s="3" t="s">
         <v>8</v>
@@ -1465,8 +1488,8 @@
       <c r="AA15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB15" s="3">
-        <v>0</v>
+      <c r="AB15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC15" s="3">
         <v>0</v>
@@ -1483,8 +1506,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1515,198 +1541,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>284100</v>
+      </c>
+      <c r="E17" s="3">
         <v>445300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>390500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>357300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>362300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>497900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>413800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>382100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>390100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>557000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>444000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>396600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>379800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>509800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>418000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>295800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>525100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>715600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>548600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>499700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>485200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>719600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>586200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>575600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>598100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>869600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>689200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1026600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>627100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>893000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>706800</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-29200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-24000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-46400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-35300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-37300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>22500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-10900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-14200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>47200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>47800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>14300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-16800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>18300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>17500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-36800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-134400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-4000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-9100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-19900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>67300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>22600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-28900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>51200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-429800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-45300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>66200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>31200</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1740,483 +1773,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E20" s="3">
         <v>1800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>7100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-15400</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-500</v>
       </c>
       <c r="N20" s="3">
         <v>-500</v>
       </c>
       <c r="O20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="P20" s="3">
         <v>1900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1600</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-7300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>5000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>25900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>5300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>3900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>5600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>7600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-20800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-17500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-44900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-23300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-29500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>26300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-6800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-6500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>38100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>54300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>21300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-6000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>29900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>27800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-25200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-129400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>14000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>16100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>20400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>93100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>35800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>15500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-14200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>72900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>22800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-406600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-18700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>95200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>56300</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E22" s="3">
         <v>5700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>5800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>5000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>5800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>5100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>4300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>4000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>4800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>6400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>7300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>8500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>8000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>7900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>7500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>7000</v>
-      </c>
-      <c r="U22" s="3">
-        <v>7400</v>
       </c>
       <c r="V22" s="3">
         <v>7400</v>
       </c>
       <c r="W22" s="3">
+        <v>7400</v>
+      </c>
+      <c r="X22" s="3">
         <v>8100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>10800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>9900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>11100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>10700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>11100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>12100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>11600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>8400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>7500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>7000</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-30400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-27800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-55200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-33500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-39600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>15500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-16900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-16700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>27100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>40900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-22200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>11400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>9500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-43800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-149100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-6000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-18000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-5200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>61800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>9900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-10600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-40900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>42400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-8700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-439400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-48000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>66300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>25800</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E24" s="3">
         <v>600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-7200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>9200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>8100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>15200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-6800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-20800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-63700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>6900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>9600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>13900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>6600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>87000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-96300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>15500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2310,198 +2359,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-24300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-28400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-60800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-26300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-41200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>6300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-18900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-21300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>19800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>31900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-24300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>16200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-23000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-85400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-6700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-24900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-6600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-11800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>47900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>5900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-7200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-47500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-44600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-5500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-343100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-46800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>50800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-24300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-28200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-61100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-26500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-41300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-19100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-21500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>19600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>31400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-24400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>16000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-22500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-85600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-6900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-25900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-7300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-12200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>47600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>5000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-7800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-48300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-46300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-5400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-344700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-48200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>49700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2595,8 +2653,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2654,8 +2715,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2672,11 +2733,11 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-33600</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2690,8 +2751,11 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2785,8 +2849,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2880,198 +2947,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-7100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>15400</v>
-      </c>
-      <c r="M32" s="3">
-        <v>500</v>
       </c>
       <c r="N32" s="3">
         <v>500</v>
       </c>
       <c r="O32" s="3">
+        <v>500</v>
+      </c>
+      <c r="P32" s="3">
         <v>-1900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>7300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-5000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-25900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-5600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-7600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-24300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-28200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-61100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-26500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-41300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-19100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-21500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>19600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>31400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-24400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>16000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-22500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-85600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-6900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-25900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-7300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-12200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>47600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>5000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-7800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-48300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-79900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-5400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-344700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-48200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>49700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3165,203 +3241,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-24300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-28200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-61100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-26500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-41300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-19100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-21500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>19600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>31400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-24400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>16000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-22500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-85600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-6900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-25900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-7300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-12200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>47600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>5000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-7800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-48300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-79900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-5400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-344700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-48200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>49700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E38" s="2">
         <v>45290</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45108</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45017</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44835</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44744</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44653</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44562</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44471</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44380</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44289</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44198</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44107</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44016</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43925</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43827</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43736</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43645</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43554</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43463</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43372</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43099</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42917</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42826</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3395,8 +3480,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3430,103 +3516,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>112900</v>
+      </c>
+      <c r="E41" s="3">
         <v>117200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>116100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>132100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>127100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>198700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>162600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>167100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>162600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>250800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>181800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>252300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>246700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>316000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>323600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>277600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>245400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>200200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>147500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>226600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>271400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>403400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>236100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>241800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>229900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>231200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>166900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>319800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>320700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>297300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>236000</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3620,388 +3710,403 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>134400</v>
+      </c>
+      <c r="E43" s="3">
         <v>187900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>194000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>162700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>168900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>206100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>215000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>176500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>201100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>255100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>251500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>187600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>175500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>229800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>189800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>130100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>153400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>289700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>247600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>204200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>199900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>328000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>261700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>204700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>234200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>367000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>310900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>240400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>245300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>375500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>321300</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>224100</v>
+      </c>
+      <c r="E44" s="3">
         <v>252800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>326700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>323900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>336500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>376000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>452700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>437900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>385800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>346900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>398300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>352000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>322500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>295300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>359500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>375900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>439700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>452300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>570300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>460300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>384100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>377600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>521300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>497800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>530700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>573800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>683000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>618100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>571500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>542500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>699600</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>165900</v>
+      </c>
+      <c r="E45" s="3">
         <v>152700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>148100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>178800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>171900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>164400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>185000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>183300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>187700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>169900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>155800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>157300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>202400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>149400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>134900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>98100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>128600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>117200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>126400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>124400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>133100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>149600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>129400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>125000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>161700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>118900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>125500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>126500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>142800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>132000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>132700</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>637300</v>
+      </c>
+      <c r="E46" s="3">
         <v>710700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>784900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>797600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>804500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>945300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1015300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>964800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>937200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1022800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>987500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>949200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>947100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>990500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1007800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>881700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>967100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1059500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1091700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1015500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>988500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1258600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1148500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1069300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1156400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1291000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1286300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1304800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1280300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1347300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1389600</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4020,47 +4125,47 @@
       <c r="H47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I47" s="3">
-        <v>300</v>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J47" s="3">
         <v>300</v>
       </c>
       <c r="K47" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="L47" s="3">
         <v>400</v>
       </c>
       <c r="M47" s="3">
+        <v>400</v>
+      </c>
+      <c r="N47" s="3">
         <v>5400</v>
-      </c>
-      <c r="N47" s="3">
-        <v>6800</v>
       </c>
       <c r="O47" s="3">
         <v>6800</v>
       </c>
       <c r="P47" s="3">
+        <v>6800</v>
+      </c>
+      <c r="Q47" s="3">
         <v>59100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>58000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>90400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>67000</v>
-      </c>
-      <c r="T47" s="3">
-        <v>7000</v>
       </c>
       <c r="U47" s="3">
         <v>7000</v>
       </c>
       <c r="V47" s="3">
-        <v>7600</v>
+        <v>7000</v>
       </c>
       <c r="W47" s="3">
         <v>7600</v>
@@ -4069,7 +4174,7 @@
         <v>7600</v>
       </c>
       <c r="Y47" s="3">
-        <v>1000</v>
+        <v>7600</v>
       </c>
       <c r="Z47" s="3">
         <v>1000</v>
@@ -4081,13 +4186,13 @@
         <v>1000</v>
       </c>
       <c r="AC47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AD47" s="3">
         <v>900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>7400</v>
-      </c>
-      <c r="AE47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF47" s="3" t="s">
         <v>8</v>
@@ -4095,198 +4200,207 @@
       <c r="AG47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>196700</v>
+      </c>
+      <c r="E48" s="3">
         <v>208200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>223100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>220800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>225700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>236800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>233800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>249200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>251800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>267400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>280700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>297100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>316800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>340800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>363000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>387200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>407800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>439700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>447100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>470600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>484700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>183200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>190600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>200100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>208500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>219700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>243400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>255800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>260400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>273900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>290800</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E49" s="3">
         <v>11400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>12400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>13000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>13600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>15000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>15800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>16500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>17800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>19300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>20800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>22400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>26900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>28000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>46400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>48100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>68300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>71300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>74300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>83900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>86700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>89500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>92500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>499800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>502400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>515800</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4380,8 +4494,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4475,103 +4592,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>45900</v>
+      </c>
+      <c r="E52" s="3">
         <v>47700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>43700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>43300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>44000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>44100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>53100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>56100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>62300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>63900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>67400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>68600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>61900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>70400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>74300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>71300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>68200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>71700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>66800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>68100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>61100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>57600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>58100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>61600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>65900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>59900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>130100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>115500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>61100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>63400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>61500</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4665,103 +4788,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>891000</v>
+      </c>
+      <c r="E54" s="3">
         <v>978000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1063200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1073400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1086000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1238100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1315000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1283400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1265300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1368700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1356000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1337400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1349100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1478500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1522300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1451300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1532600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1604700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1640600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1608200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1589900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1575200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1469500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1406200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1515700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1658400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1750400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1776000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2101700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2186900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2257600</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4795,8 +4924,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4830,103 +4960,107 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>142900</v>
+      </c>
+      <c r="E57" s="3">
         <v>147200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>158000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>139800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>120100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>191100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>204000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>208700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>198500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>229900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>246300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>213500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>201200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>178200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>213100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>127900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>132700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>172200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>193000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>178500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>138300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>169600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>159400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>139500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>133700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>205000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>248800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>163500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>151200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>163600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>193600</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4937,19 +5071,19 @@
         <v>500</v>
       </c>
       <c r="F58" s="3">
+        <v>500</v>
+      </c>
+      <c r="G58" s="3">
         <v>400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>400</v>
-      </c>
-      <c r="J58" s="3">
-        <v>600</v>
       </c>
       <c r="K58" s="3">
         <v>600</v>
@@ -4958,61 +5092,61 @@
         <v>600</v>
       </c>
       <c r="M58" s="3">
+        <v>600</v>
+      </c>
+      <c r="N58" s="3">
         <v>41200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>38400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>37900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>41600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>21400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>25200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>21100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>26200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>21900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>66400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>65900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>126400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>128000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>127700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>127100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>40200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>32700</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>26400</v>
       </c>
       <c r="AF58" s="3">
         <v>26400</v>
@@ -5020,388 +5154,403 @@
       <c r="AG58" s="3">
         <v>26400</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>26400</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>152000</v>
+      </c>
+      <c r="E59" s="3">
         <v>194800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>190100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>181200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>184600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>234400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>224300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>212000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>233500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>305200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>281900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>269900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>268100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>338800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>315400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>310600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>309400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>360800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>314300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>282700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>292400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>309800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>283800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>240300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>263100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>302000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>264500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>217800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>209100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>224600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>204200</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>295400</v>
+      </c>
+      <c r="E60" s="3">
         <v>342500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>348600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>321500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>305100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>425900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>428700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>421300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>432700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>535600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>569400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>521800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>507200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>558500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>549900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>463700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>463200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>559200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>529100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>527600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>496500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>605800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>571200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>507500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>523900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>509100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>553500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>414100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>386700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>414600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>424100</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>202900</v>
+      </c>
+      <c r="E61" s="3">
         <v>207000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>255900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>243000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>234600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>216100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>293600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>248900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>183900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>141400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>97400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>139700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>157200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>185900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>217900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>243900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>298500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>178800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>242100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>162000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>161100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>269800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>269100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>268400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>335500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>443900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>444300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>613600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>589700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>610000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>697400</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>166100</v>
+      </c>
+      <c r="E62" s="3">
         <v>176800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>180000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>171900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>180000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>193100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>202400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>219200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>219300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>226400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>246300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>266600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>275800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>294100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>331000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>347100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>354500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>362900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>359500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>379000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>383000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>111000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>99600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>113500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>129700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>124400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>99600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>93500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>142900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>146900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>151100</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5495,8 +5644,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5590,8 +5742,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5685,103 +5840,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>661900</v>
+      </c>
+      <c r="E66" s="3">
         <v>723800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>782100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>733900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>716900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>832200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>921900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>886200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>838200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>905500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>915000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>929600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>941300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1039400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1099500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1055300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1117100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1101700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1131400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1069000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1044200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>989700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>942700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>891200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>994200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1082200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1109100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1132900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1129800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1180700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1284900</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5815,8 +5976,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5910,8 +6072,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6005,8 +6170,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6100,8 +6268,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6195,103 +6366,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E72" s="3">
         <v>18400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>46600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>107700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>134200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>175500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>184900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>179100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>198100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>229100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>209500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>178100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>179300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>203700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>207700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>191700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>214200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>299800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>306700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>332600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>339900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>381600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>332000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>327000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>334800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>409700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>489500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>494900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>839600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>887800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>838100</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6385,8 +6562,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6480,8 +6660,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6575,103 +6758,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>229100</v>
+      </c>
+      <c r="E76" s="3">
         <v>254200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>281100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>339500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>369100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>405900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>393000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>397300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>427200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>463200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>440900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>407900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>407800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>439100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>422800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>396100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>415400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>503100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>509300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>539200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>545700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>585500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>526800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>515000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>521400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>576100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>641300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>643000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>971900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1006200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>972700</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6765,203 +6954,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E80" s="2">
         <v>45290</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45108</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45017</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44835</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44744</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44653</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44562</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44471</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44380</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44289</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44198</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44107</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44016</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43925</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43827</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43736</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43645</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43554</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43463</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43372</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43099</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42917</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42826</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-24300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-28200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-61100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-26500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-41300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-19100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-21500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>19600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>31400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-24400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>16000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-22500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-85600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-6900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-25900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-7300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-12200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>47600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>5000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-7800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-48300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-79900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-5400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-344700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-48200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>49700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6995,103 +7193,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>4600</v>
+        <v>4500</v>
       </c>
       <c r="E83" s="3">
         <v>4600</v>
       </c>
       <c r="F83" s="3">
+        <v>4600</v>
+      </c>
+      <c r="G83" s="3">
         <v>4800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5800</v>
-      </c>
-      <c r="K83" s="3">
-        <v>6200</v>
       </c>
       <c r="L83" s="3">
         <v>6200</v>
       </c>
       <c r="M83" s="3">
+        <v>6200</v>
+      </c>
+      <c r="N83" s="3">
         <v>7000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>8900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>10000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>10300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>10700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>12200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>12900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>13500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>13900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>14400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>20400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>16100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>15100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>16000</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>19400</v>
       </c>
       <c r="AC83" s="3">
         <v>19400</v>
       </c>
       <c r="AD83" s="3">
+        <v>19400</v>
+      </c>
+      <c r="AE83" s="3">
         <v>21200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>20900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>21400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7185,8 +7387,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7280,8 +7485,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7375,8 +7583,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7470,8 +7681,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7565,103 +7779,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>600</v>
+      </c>
+      <c r="E89" s="3">
         <v>48500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-24900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-85900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>103900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-49000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-50700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-115000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>87000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-27200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>28100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-37800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>84200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>88800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-77100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>124000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-112100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-33700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>7600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>175700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>81700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>119400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>24800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-16000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>51400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>150800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-12600</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7695,103 +7915,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-6800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-6600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-7800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-8300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-8400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-8800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-12200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-14200</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7885,8 +8109,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7980,103 +8207,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>15100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-7600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>35300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-8500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-7800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-7500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>30100</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8110,8 +8343,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8205,8 +8439,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8300,8 +8537,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8395,8 +8635,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8490,289 +8733,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-49400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>12500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>16500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-79200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>44000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>56100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>32100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-15100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-41200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-22100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-34200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-14900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-32900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-53700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>112300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-66300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>36300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-6100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-172400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-71700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>12000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-45200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-162900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>28500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-22000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-92600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-12300</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>700</v>
+      </c>
+      <c r="E101" s="3">
         <v>3200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>6600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>3200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1300</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-6600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>12500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>2600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>600</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>-2300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>4800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>3500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>4700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-10600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>10800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E102" s="3">
         <v>900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-16200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-71800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>30400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-88800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>68800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-71300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>6300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-63500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>46400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>32500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>44500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>52700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-79400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-44600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-131800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>173100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-5800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>11900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>64300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-152900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>23500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>61400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>4100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FOSL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FOSL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
   <si>
     <t>FOSL</t>
   </si>
@@ -656,433 +656,446 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E7" s="2">
         <v>45381</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45290</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45108</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45017</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44835</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44744</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44653</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44562</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44471</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44380</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44289</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44198</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44107</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44016</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43925</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43827</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43736</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43645</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43554</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43463</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43372</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43099</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42917</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42826</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>260000</v>
+      </c>
+      <c r="E8" s="3">
         <v>254900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>421300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>344100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>322000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>325000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>499100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>436300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>371200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>375900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>604200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>491800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>410900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>363000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>528100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>435500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>259000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>390700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>711600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>539500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>501400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>465300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>786900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>608800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>576600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>569200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>920800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>688700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>596800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>581800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>959200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>738000</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>123100</v>
+      </c>
+      <c r="E9" s="3">
         <v>121600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>222000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>183800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>162400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>159100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>263800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>216700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>179800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>191500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>301800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>232300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>189100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>180500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>268500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>205700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>118400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>250400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>403700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>260900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>236300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>217300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>370000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>282300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>267600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>281500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>472700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>368800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>295500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>292300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>470100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>352900</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>136900</v>
+      </c>
+      <c r="E10" s="3">
         <v>133300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>199300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>160300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>159600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>165900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>235400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>219600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>191400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>184400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>302400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>259500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>221800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>182500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>259600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>229800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>140600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>140300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>307900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>278600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>265100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>248000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>416900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>326500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>309000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>287700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>448100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>319900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>301300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>289500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>489100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>385100</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1117,8 +1130,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1215,8 +1229,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1313,106 +1330,112 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E14" s="3">
         <v>10200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>15600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>15300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>7700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>12400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>6100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>6000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>7000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>12000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>17800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>9700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>14100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>28600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>12800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>25100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>9000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>11000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>4800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>6200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>21000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>23500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>6400</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>5800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>416900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>26300</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>13300</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1446,8 +1469,8 @@
       <c r="M15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N15" s="3">
-        <v>100</v>
+      <c r="N15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O15" s="3">
         <v>100</v>
@@ -1477,10 +1500,10 @@
         <v>100</v>
       </c>
       <c r="X15" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y15" s="3">
         <v>400</v>
-      </c>
-      <c r="Y15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>8</v>
@@ -1491,8 +1514,8 @@
       <c r="AB15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC15" s="3">
-        <v>0</v>
+      <c r="AC15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD15" s="3">
         <v>0</v>
@@ -1509,8 +1532,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1542,204 +1568,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>294000</v>
+      </c>
+      <c r="E17" s="3">
         <v>284100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>445300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>390500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>357300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>362300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>497900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>413800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>382100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>390100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>557000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>444000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>396600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>379800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>509800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>418000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>295800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>525100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>715600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>548600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>499700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>485200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>719600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>586200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>575600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>598100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>869600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>689200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1026600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>627100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>893000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>706800</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-34000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-29200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-24000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-46400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-35300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-37300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>22500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-10900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-14200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>47200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>47800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>14300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-16800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>18300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>17500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-36800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-134400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-4000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-9100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-19900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>67300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>22600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-28900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>51200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-429800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-45300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>66200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>31200</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1774,498 +1807,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E20" s="3">
         <v>3900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>7100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-15400</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-500</v>
       </c>
       <c r="O20" s="3">
         <v>-500</v>
       </c>
       <c r="P20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Q20" s="3">
         <v>1900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1600</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-7300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>5000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>25900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>5300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>3900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>5600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>7600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-28600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-20800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-17500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-44900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-23300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-29500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>26300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-6800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-6500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>38100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>54300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>21300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>29900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>27800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-25200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-129400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>14000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>16100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>20400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>93100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>35800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>15500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-14200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>72900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>22800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-406600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-18700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>95200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>56300</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E22" s="3">
         <v>5100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>5700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>5300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>5000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>5800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>4300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>4000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>4800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>7300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>8500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>8000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>7900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>7500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>7000</v>
-      </c>
-      <c r="V22" s="3">
-        <v>7400</v>
       </c>
       <c r="W22" s="3">
         <v>7400</v>
       </c>
       <c r="X22" s="3">
+        <v>7400</v>
+      </c>
+      <c r="Y22" s="3">
         <v>8100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>10800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>9900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>11100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>10700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>11100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>12100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>11600</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>8400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>7500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>7000</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-36600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-30400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-27800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-55200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-33500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-39600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-4000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>15500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-16900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-16700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>27100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>40900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-22200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>11400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>9500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-43800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-149100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-6000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-18000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>61800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>9900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-10600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-40900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>42400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-8700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-439400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-48000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>66300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>25800</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-6100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-7200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>9200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>9000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>8100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>15200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-6800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-20800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-63700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>6900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>9600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>13900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>3900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>6600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>87000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-96300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>15500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2362,204 +2411,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-38800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-24300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-28400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-60800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-26300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-41200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-9500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-18900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-21300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>19800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>31900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-24300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>16200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-23000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-85400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-6700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-24900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-6600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-11800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>47900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>5900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-7200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-47500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-44600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-5500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-343100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-46800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>50800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-38800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-24300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-28200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-61100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-26500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-41300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-19100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-21500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>19600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>31400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-24400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>16000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-22500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-85600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-6900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-25900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-7300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-12200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>47600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>5000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-7800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-48300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-46300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-5400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-344700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-48200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>49700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2656,8 +2714,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2718,8 +2779,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2736,11 +2797,11 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-33600</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2754,8 +2815,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2852,8 +2916,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2950,204 +3017,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-7100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>15400</v>
-      </c>
-      <c r="N32" s="3">
-        <v>500</v>
       </c>
       <c r="O32" s="3">
         <v>500</v>
       </c>
       <c r="P32" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1600</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>7300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-5000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-25900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-5300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-5600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-7600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-38800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-24300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-28200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-61100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-26500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-41300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-19100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-21500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>19600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>31400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-24400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>16000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-22500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-85600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-6900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-25900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-7300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-12200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>47600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>5000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-7800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-48300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-79900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-5400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-344700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-48200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>49700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3244,209 +3320,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-38800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-24300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-28200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-61100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-26500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-41300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-19100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-21500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>19600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>31400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-24400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>16000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-22500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-85600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-6900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-25900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-7300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-12200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>47600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>5000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-7800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-48300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-79900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-5400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-344700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-48200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>49700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E38" s="2">
         <v>45381</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45290</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45108</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45017</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44835</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44744</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44653</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44562</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44471</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44380</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44289</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44198</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44107</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44016</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43925</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43827</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43736</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43645</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43554</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43463</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43372</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43099</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42917</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42826</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3481,8 +3566,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3517,106 +3603,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>104900</v>
+      </c>
+      <c r="E41" s="3">
         <v>112900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>117200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>116100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>132100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>127100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>198700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>162600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>167100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>162600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>250800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>181800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>252300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>246700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>316000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>323600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>277600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>245400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>200200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>147500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>226600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>271400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>403400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>236100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>241800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>229900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>231200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>166900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>319800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>320700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>297300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>236000</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3713,400 +3803,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>133100</v>
+      </c>
+      <c r="E43" s="3">
         <v>134400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>187900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>194000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>162700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>168900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>206100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>215000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>176500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>201100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>255100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>251500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>187600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>175500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>229800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>189800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>130100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>153400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>289700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>247600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>204200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>199900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>328000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>261700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>204700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>234200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>367000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>310900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>240400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>245300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>375500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>321300</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>202100</v>
+      </c>
+      <c r="E44" s="3">
         <v>224100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>252800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>326700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>323900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>336500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>376000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>452700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>437900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>385800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>346900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>398300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>352000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>322500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>295300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>359500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>375900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>439700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>452300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>570300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>460300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>384100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>377600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>521300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>497800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>530700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>573800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>683000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>618100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>571500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>542500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>699600</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>102300</v>
+      </c>
+      <c r="E45" s="3">
         <v>165900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>152700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>148100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>178800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>171900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>164400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>185000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>183300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>187700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>169900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>155800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>157300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>202400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>149400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>134900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>98100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>128600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>117200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>126400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>124400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>133100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>149600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>129400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>125000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>161700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>118900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>125500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>126500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>142800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>132000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>132700</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>542400</v>
+      </c>
+      <c r="E46" s="3">
         <v>637300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>710700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>784900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>797600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>804500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>945300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1015300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>964800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>937200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1022800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>987500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>949200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>947100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>990500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1007800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>881700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>967100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1059500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1091700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1015500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>988500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1258600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1148500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1069300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1156400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1291000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1286300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1304800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1280300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1347300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1389600</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4128,47 +4233,47 @@
       <c r="I47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="3">
-        <v>300</v>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>300</v>
       </c>
       <c r="L47" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="M47" s="3">
         <v>400</v>
       </c>
       <c r="N47" s="3">
+        <v>400</v>
+      </c>
+      <c r="O47" s="3">
         <v>5400</v>
-      </c>
-      <c r="O47" s="3">
-        <v>6800</v>
       </c>
       <c r="P47" s="3">
         <v>6800</v>
       </c>
       <c r="Q47" s="3">
+        <v>6800</v>
+      </c>
+      <c r="R47" s="3">
         <v>59100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>58000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>90400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>67000</v>
-      </c>
-      <c r="U47" s="3">
-        <v>7000</v>
       </c>
       <c r="V47" s="3">
         <v>7000</v>
       </c>
       <c r="W47" s="3">
-        <v>7600</v>
+        <v>7000</v>
       </c>
       <c r="X47" s="3">
         <v>7600</v>
@@ -4177,7 +4282,7 @@
         <v>7600</v>
       </c>
       <c r="Z47" s="3">
-        <v>1000</v>
+        <v>7600</v>
       </c>
       <c r="AA47" s="3">
         <v>1000</v>
@@ -4189,13 +4294,13 @@
         <v>1000</v>
       </c>
       <c r="AD47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AE47" s="3">
         <v>900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>7400</v>
-      </c>
-      <c r="AF47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG47" s="3" t="s">
         <v>8</v>
@@ -4203,204 +4308,213 @@
       <c r="AH47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>187400</v>
+      </c>
+      <c r="E48" s="3">
         <v>196700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>208200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>223100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>220800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>225700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>236800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>233800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>249200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>251800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>267400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>280700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>297100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>316800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>340800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>363000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>387200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>407800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>439700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>447100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>470600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>484700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>183200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>190600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>200100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>208500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>219700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>243400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>255800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>260400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>273900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>290800</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E49" s="3">
         <v>11100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>12400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>13000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>13600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>15000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>15800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>16500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>17800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>19300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>20800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>22400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>26900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>28000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>46400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>48100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>68300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>71300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>74300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>83900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>86700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>89500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>92500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>499800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>502400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>515800</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4497,8 +4611,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4595,106 +4712,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E52" s="3">
         <v>45900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>47700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>43700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>43300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>44000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>44100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>53100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>56100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>62300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>63900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>67400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>68600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>61900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>70400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>74300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>71300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>68200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>71700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>66800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>68100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>61100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>57600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>58100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>61600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>65900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>59900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>130100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>115500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>61100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>63400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>61500</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4791,106 +4914,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>785700</v>
+      </c>
+      <c r="E54" s="3">
         <v>891000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>978000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1063200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1073400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1086000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1238100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1315000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1283400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1265300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1368700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1356000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1337400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1349100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1478500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1522300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1451300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1532600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1604700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1640600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1608200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1589900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1575200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1469500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1406200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1515700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1658400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1750400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1776000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2101700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2186900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2257600</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4925,8 +5054,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4961,111 +5091,115 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>132500</v>
+      </c>
+      <c r="E57" s="3">
         <v>142900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>147200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>158000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>139800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>120100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>191100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>204000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>208700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>198500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>229900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>246300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>213500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>201200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>178200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>213100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>127900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>132700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>172200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>193000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>178500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>138300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>169600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>159400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>139500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>133700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>205000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>248800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>163500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>151200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>163600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>193600</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>500</v>
+        <v>2600</v>
       </c>
       <c r="E58" s="3">
         <v>500</v>
@@ -5074,19 +5208,19 @@
         <v>500</v>
       </c>
       <c r="G58" s="3">
+        <v>500</v>
+      </c>
+      <c r="H58" s="3">
         <v>400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>400</v>
-      </c>
-      <c r="K58" s="3">
-        <v>600</v>
       </c>
       <c r="L58" s="3">
         <v>600</v>
@@ -5095,61 +5229,61 @@
         <v>600</v>
       </c>
       <c r="N58" s="3">
+        <v>600</v>
+      </c>
+      <c r="O58" s="3">
         <v>41200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>38400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>37900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>41600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>21400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>25200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>21100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>26200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>21900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>66400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>65900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>126400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>128000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>127700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>127100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>40200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>32700</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>26400</v>
       </c>
       <c r="AG58" s="3">
         <v>26400</v>
@@ -5157,400 +5291,415 @@
       <c r="AH58" s="3">
         <v>26400</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>26400</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>144600</v>
+      </c>
+      <c r="E59" s="3">
         <v>152000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>194800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>190100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>181200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>184600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>234400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>224300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>212000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>233500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>305200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>281900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>269900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>268100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>338800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>315400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>310600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>309400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>360800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>314300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>282700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>292400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>309800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>283800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>240300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>263100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>302000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>264500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>217800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>209100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>224600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>204200</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>279700</v>
+      </c>
+      <c r="E60" s="3">
         <v>295400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>342500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>348600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>321500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>305100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>425900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>428700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>421300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>432700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>535600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>569400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>521800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>507200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>558500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>549900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>463700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>463200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>559200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>529100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>527600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>496500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>605800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>571200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>507500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>523900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>509100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>553500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>414100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>386700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>414600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>424100</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>156500</v>
+      </c>
+      <c r="E61" s="3">
         <v>202900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>207000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>255900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>243000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>234600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>216100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>293600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>248900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>183900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>141400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>97400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>139700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>157200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>185900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>217900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>243900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>298500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>178800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>242100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>162000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>161100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>269800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>269100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>268400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>335500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>443900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>444300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>613600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>589700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>610000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>697400</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>162400</v>
+      </c>
+      <c r="E62" s="3">
         <v>166100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>176800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>180000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>171900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>180000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>193100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>202400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>219200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>219300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>226400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>246300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>266600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>275800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>294100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>331000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>347100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>354500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>362900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>359500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>379000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>383000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>111000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>99600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>113500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>129700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>124400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>99600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>93500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>142900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>146900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>151100</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5647,8 +5796,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5745,8 +5897,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5843,106 +5998,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>596000</v>
+      </c>
+      <c r="E66" s="3">
         <v>661900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>723800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>782100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>733900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>716900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>832200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>921900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>886200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>838200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>905500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>915000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>929600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>941300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1039400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1099500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1055300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1117100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1101700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1131400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1069000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1044200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>989700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>942700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>891200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>994200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1082200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1109100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1132900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1129800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1180700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1284900</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5977,8 +6138,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6075,8 +6237,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6173,8 +6338,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6271,8 +6439,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6369,106 +6540,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-44700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-5900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>18400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>46600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>107700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>134200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>175500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>184900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>179100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>198100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>229100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>209500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>178100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>179300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>203700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>207700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>191700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>214200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>299800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>306700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>332600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>339900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>381600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>332000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>327000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>334800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>409700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>489500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>494900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>839600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>887800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>838100</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6565,8 +6742,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6663,8 +6843,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6761,106 +6944,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>189600</v>
+      </c>
+      <c r="E76" s="3">
         <v>229100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>254200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>281100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>339500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>369100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>405900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>393000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>397300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>427200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>463200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>440900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>407900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>407800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>439100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>422800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>396100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>415400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>503100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>509300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>539200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>545700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>585500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>526800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>515000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>521400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>576100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>641300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>643000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>971900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1006200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>972700</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6957,209 +7146,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E80" s="2">
         <v>45381</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45290</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45108</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45017</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44835</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44744</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44653</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44562</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44471</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44380</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44289</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44198</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44107</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44016</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43925</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43827</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43736</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43645</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43554</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43463</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43372</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43099</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42917</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42826</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-38800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-24300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-28200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-61100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-26500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-41300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-19100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-21500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>19600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>31400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-24400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>16000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-22500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-85600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-6900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-25900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-7300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-12200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>47600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>5000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-7800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-48300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-79900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-5400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-344700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-48200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>49700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7194,106 +7392,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E83" s="3">
         <v>4500</v>
-      </c>
-      <c r="E83" s="3">
-        <v>4600</v>
       </c>
       <c r="F83" s="3">
         <v>4600</v>
       </c>
       <c r="G83" s="3">
+        <v>4600</v>
+      </c>
+      <c r="H83" s="3">
         <v>4800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5800</v>
-      </c>
-      <c r="L83" s="3">
-        <v>6200</v>
       </c>
       <c r="M83" s="3">
         <v>6200</v>
       </c>
       <c r="N83" s="3">
+        <v>6200</v>
+      </c>
+      <c r="O83" s="3">
         <v>7000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>8900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>10000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>10300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>10700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>12200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>12900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>13500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>13900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>14400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>20400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>16100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>15100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>16000</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>19400</v>
       </c>
       <c r="AD83" s="3">
         <v>19400</v>
       </c>
       <c r="AE83" s="3">
+        <v>19400</v>
+      </c>
+      <c r="AF83" s="3">
         <v>21200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>20900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>21400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7390,8 +7592,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7488,8 +7693,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7586,8 +7794,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7684,8 +7895,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7782,106 +7996,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E89" s="3">
         <v>600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>48500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-24900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-85900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>103900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-49000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-50700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-115000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>87000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-27200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>28100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-37800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>84200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>88800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-77100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>124000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-112100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-33700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>7600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>175700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-4900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>81700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>119400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>24800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-16000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>51400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>150800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-12600</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7916,8 +8136,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7925,97 +8146,100 @@
         <v>-1700</v>
       </c>
       <c r="E91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-6800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-6600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-7800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-8300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-8400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-8800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-12200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-14200</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8112,8 +8336,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8210,106 +8437,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>15100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-7600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>35300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-8500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-4100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-7800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-4300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-7500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>30100</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8344,8 +8577,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8442,8 +8676,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8540,8 +8777,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8638,8 +8878,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8736,298 +8979,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-44800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-49400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>12500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>6800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>16500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-79200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>44000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>56100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>32100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-15100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-41200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-22100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-34200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-14900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-32900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-53700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>112300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-66300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>36300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-6100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-172400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-71700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>12000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-45200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-162900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>28500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-22000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-92600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-12300</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>400</v>
+      </c>
+      <c r="E101" s="3">
         <v>700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>3200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>6600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>3200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1300</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>1000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-6600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>4100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>12500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>2600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>600</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>4800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>3500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>4700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-10600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>10800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-16200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>4700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-71800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>30400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>3500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-88800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>68800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-71300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-63500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>46400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>32500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>44500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>52700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-79400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-44600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-131800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>173100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>11900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>64300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-152900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>23500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>61400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>4100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FOSL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FOSL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
   <si>
     <t>FOSL</t>
   </si>
@@ -656,446 +656,459 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E7" s="2">
         <v>45472</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45381</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45290</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45108</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45017</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44835</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44744</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44653</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44562</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44471</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44380</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44289</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44198</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44107</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44016</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43925</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43827</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43736</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43645</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43554</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43463</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43372</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43099</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42917</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42826</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>287800</v>
+      </c>
+      <c r="E8" s="3">
         <v>260000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>254900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>421300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>344100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>322000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>325000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>499100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>436300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>371200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>375900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>604200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>491800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>410900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>363000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>528100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>435500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>259000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>390700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>711600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>539500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>501400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>465300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>786900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>608800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>576600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>569200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>920800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>688700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>596800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>581800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>959200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>738000</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>145600</v>
+      </c>
+      <c r="E9" s="3">
         <v>123100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>121600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>222000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>183800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>162400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>159100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>263800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>216700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>179800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>191500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>301800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>232300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>189100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>180500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>268500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>205700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>118400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>250400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>403700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>260900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>236300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>217300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>370000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>282300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>267600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>281500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>472700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>368800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>295500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>292300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>470100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>352900</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>142200</v>
+      </c>
+      <c r="E10" s="3">
         <v>136900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>133300</v>
       </c>
-      <c r="F10" s="3">
-        <v>199300</v>
-      </c>
       <c r="G10" s="3">
+        <v>199200</v>
+      </c>
+      <c r="H10" s="3">
         <v>160300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>159600</v>
       </c>
-      <c r="I10" s="3">
-        <v>165900</v>
-      </c>
       <c r="J10" s="3">
+        <v>166000</v>
+      </c>
+      <c r="K10" s="3">
         <v>235400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>219600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>191400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>184400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>302400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>259500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>221800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>182500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>259600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>229800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>140600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>140300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>307900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>278600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>265100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>248000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>416900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>326500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>309000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>287700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>448100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>319900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>301300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>289500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>489100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>385100</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1131,8 +1144,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1145,8 +1159,8 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
+      <c r="G12" s="3">
+        <v>19400</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
@@ -1232,8 +1246,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1333,132 +1350,138 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E14" s="3">
         <v>17300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>10200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>15600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>15300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>7700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>12400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>6100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>6000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>7000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>12000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>17800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>9700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>14100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>28600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>12800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>25100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>9000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>11000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>4800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>6200</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>21000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>23500</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>6400</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>5800</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>416900</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>26300</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>13300</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>8</v>
+      <c r="D15" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E15" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F15" s="3">
+        <v>4500</v>
+      </c>
+      <c r="G15" s="3">
+        <v>4600</v>
+      </c>
+      <c r="H15" s="3">
+        <v>4600</v>
+      </c>
+      <c r="I15" s="3">
+        <v>4800</v>
+      </c>
+      <c r="J15" s="3">
+        <v>5100</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>8</v>
@@ -1472,8 +1495,8 @@
       <c r="N15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O15" s="3">
-        <v>100</v>
+      <c r="O15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P15" s="3">
         <v>100</v>
@@ -1503,10 +1526,10 @@
         <v>100</v>
       </c>
       <c r="Y15" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z15" s="3">
         <v>400</v>
-      </c>
-      <c r="Z15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA15" s="3" t="s">
         <v>8</v>
@@ -1517,8 +1540,8 @@
       <c r="AC15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD15" s="3">
-        <v>0</v>
+      <c r="AD15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE15" s="3">
         <v>0</v>
@@ -1535,8 +1558,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1569,210 +1595,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>294000</v>
+        <v>306400</v>
       </c>
       <c r="E17" s="3">
-        <v>284100</v>
+        <v>276700</v>
       </c>
       <c r="F17" s="3">
-        <v>445300</v>
+        <v>273900</v>
       </c>
       <c r="G17" s="3">
-        <v>390500</v>
+        <v>429700</v>
       </c>
       <c r="H17" s="3">
-        <v>357300</v>
+        <v>375200</v>
       </c>
       <c r="I17" s="3">
-        <v>362300</v>
+        <v>349600</v>
       </c>
       <c r="J17" s="3">
+        <v>349900</v>
+      </c>
+      <c r="K17" s="3">
         <v>497900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>413800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>382100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>390100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>557000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>444000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>396600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>379800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>509800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>418000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>295800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>525100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>715600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>548600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>499700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>485200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>719600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>586200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>575600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>598100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>869600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>689200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1026600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>627100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>893000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>706800</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-34000</v>
+        <v>-18600</v>
       </c>
       <c r="E18" s="3">
-        <v>-29200</v>
+        <v>-16800</v>
       </c>
       <c r="F18" s="3">
-        <v>-24000</v>
+        <v>-19000</v>
       </c>
       <c r="G18" s="3">
-        <v>-46400</v>
+        <v>-8400</v>
       </c>
       <c r="H18" s="3">
-        <v>-35300</v>
+        <v>-31100</v>
       </c>
       <c r="I18" s="3">
-        <v>-37300</v>
+        <v>-27600</v>
       </c>
       <c r="J18" s="3">
+        <v>-24900</v>
+      </c>
+      <c r="K18" s="3">
         <v>1200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>22500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-10900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-14200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>47200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>47800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>14300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-16800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>18300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>17500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-36800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-134400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-4000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-9100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-19900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>67300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>22600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-28900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>51200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-429800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-45300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>66200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>31200</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1808,513 +1841,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1400</v>
+        <v>-3600</v>
       </c>
       <c r="E20" s="3">
-        <v>3900</v>
+        <v>-1500</v>
       </c>
       <c r="F20" s="3">
-        <v>1800</v>
+        <v>-2800</v>
       </c>
       <c r="G20" s="3">
-        <v>-3100</v>
+        <v>1300</v>
       </c>
       <c r="H20" s="3">
-        <v>7100</v>
+        <v>3100</v>
       </c>
       <c r="I20" s="3">
-        <v>2800</v>
+        <v>-7200</v>
       </c>
       <c r="J20" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="K20" s="3">
         <v>500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-15400</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-500</v>
       </c>
       <c r="P20" s="3">
         <v>-500</v>
       </c>
       <c r="Q20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="R20" s="3">
         <v>1900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1600</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-7300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>5000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>25900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>5300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>3900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>5600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>7600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-28600</v>
+        <v>-11200</v>
       </c>
       <c r="E21" s="3">
-        <v>-20800</v>
+        <v>-11400</v>
       </c>
       <c r="F21" s="3">
-        <v>-17500</v>
+        <v>-11800</v>
       </c>
       <c r="G21" s="3">
-        <v>-44900</v>
+        <v>-5200</v>
       </c>
       <c r="H21" s="3">
-        <v>-23300</v>
+        <v>-29600</v>
       </c>
       <c r="I21" s="3">
-        <v>-29500</v>
+        <v>-15600</v>
       </c>
       <c r="J21" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="K21" s="3">
         <v>7500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>26300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-6800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-6500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>38100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>54300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>21300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-6000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>29900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>27800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-25200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-129400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>14000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>3000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>16100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>20400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>93100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>35800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>15500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-14200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>72900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>22800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-406600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-18700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>95200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>56300</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E22" s="3">
         <v>4100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>5100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>5800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>5300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>5000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>4300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>4000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>4800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>6500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>7300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>8500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>8000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>7900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>7500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>7000</v>
-      </c>
-      <c r="W22" s="3">
-        <v>7400</v>
       </c>
       <c r="X22" s="3">
         <v>7400</v>
       </c>
       <c r="Y22" s="3">
+        <v>7400</v>
+      </c>
+      <c r="Z22" s="3">
         <v>8100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>10800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>9900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>11100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>10700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>11100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>12100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>11600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>8400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>7500</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>7000</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-25800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-36600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-30400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-27800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-55200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-33500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-39600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>15500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-16900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-16700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>27100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>40900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-22200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>11400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>9500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-43800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-149100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-6000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-18000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>61800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>9900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-10600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-40900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>42400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-8700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-439400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-48000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>66300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>25800</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E24" s="3">
         <v>2200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-6100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-7200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>9200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>9000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>8100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>15200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-6800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-20800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-63700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>6900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>9600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>13900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>3900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>6600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>87000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-96300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>15500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2414,210 +2463,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-31900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-38800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-24300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-28400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-60800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-26300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-41200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-9500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-18900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-21300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>19800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>31900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-24300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>16200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-23000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-85400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-6700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-24900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-6600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-11800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>47900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>5900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-7200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-47500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-44600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-5500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-343100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-46800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>50800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-38800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-24300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-28200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-61100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-26500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-41300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-9400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-19100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-21500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>19600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>31400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-24400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>16000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-22500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-85600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-6900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-25900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-7300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-12200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>47600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>5000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-7800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-48300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-46300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-5400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-344700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-48200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>49700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2717,8 +2775,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2782,8 +2843,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2800,11 +2861,11 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-33600</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -2818,8 +2879,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2919,8 +2983,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3020,210 +3087,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1400</v>
+        <v>3600</v>
       </c>
       <c r="E32" s="3">
-        <v>-3900</v>
+        <v>1500</v>
       </c>
       <c r="F32" s="3">
-        <v>-1800</v>
+        <v>2800</v>
       </c>
       <c r="G32" s="3">
-        <v>3100</v>
+        <v>-1300</v>
       </c>
       <c r="H32" s="3">
-        <v>-7100</v>
+        <v>-3100</v>
       </c>
       <c r="I32" s="3">
-        <v>-2800</v>
+        <v>7200</v>
       </c>
       <c r="J32" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K32" s="3">
         <v>-500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>15400</v>
-      </c>
-      <c r="O32" s="3">
-        <v>500</v>
       </c>
       <c r="P32" s="3">
         <v>500</v>
       </c>
       <c r="Q32" s="3">
+        <v>500</v>
+      </c>
+      <c r="R32" s="3">
         <v>-1900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1600</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>7300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-5000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-25900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-5300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-5600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-7600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-38800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-24300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-28200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-61100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-26500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-41300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-9400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-19100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-21500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>19600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>31400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-24400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>16000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-22500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-85600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-6900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-25900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-7300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-12200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>47600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>5000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-7800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-48300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-79900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-5400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-344700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-48200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>49700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3323,215 +3399,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-38800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-24300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-28200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-61100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-26500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-41300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-9400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-19100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-21500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>19600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>31400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-24400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>16000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-22500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-85600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-6900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-25900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-7300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-12200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>47600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>5000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-7800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-48300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-79900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-5400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-344700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-48200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>49700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E38" s="2">
         <v>45472</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45381</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45290</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45108</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45017</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44835</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44744</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44653</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44562</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44471</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44380</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44289</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44198</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44107</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44016</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43925</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43827</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43736</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43645</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43554</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43463</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43372</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43099</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42917</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42826</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3567,8 +3652,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3604,109 +3690,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>106300</v>
+      </c>
+      <c r="E41" s="3">
         <v>104900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>112900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>117200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>116100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>132100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>127100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>198700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>162600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>167100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>162600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>250800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>181800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>252300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>246700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>316000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>323600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>277600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>245400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>200200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>147500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>226600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>271400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>403400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>236100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>241800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>229900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>231200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>166900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>319800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>320700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>297300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>236000</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3720,7 +3810,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H42" s="3">
         <v>0</v>
@@ -3806,412 +3896,427 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>173700</v>
+      </c>
+      <c r="E43" s="3">
         <v>133100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>134400</v>
       </c>
-      <c r="F43" s="3">
-        <v>187900</v>
-      </c>
       <c r="G43" s="3">
+        <v>245300</v>
+      </c>
+      <c r="H43" s="3">
         <v>194000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>162700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>168900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>206100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>215000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>176500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>201100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>255100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>251500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>187600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>175500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>229800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>189800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>130100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>153400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>289700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>247600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>204200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>199900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>328000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>261700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>204700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>234200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>367000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>310900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>240400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>245300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>375500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>321300</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>226400</v>
+      </c>
+      <c r="E44" s="3">
         <v>202100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>224100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>252800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>326700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>323900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>336500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>376000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>452700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>437900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>385800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>346900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>398300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>352000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>322500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>295300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>359500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>375900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>439700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>452300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>570300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>460300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>384100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>377600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>521300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>497800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>530700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>573800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>683000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>618100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>571500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>542500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>699600</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>102300</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
-        <v>165900</v>
+        <v>1200</v>
       </c>
       <c r="F45" s="3">
-        <v>152700</v>
+        <v>1300</v>
       </c>
       <c r="G45" s="3">
-        <v>148100</v>
+        <v>42800</v>
       </c>
       <c r="H45" s="3">
-        <v>178800</v>
+        <v>3800</v>
       </c>
       <c r="I45" s="3">
-        <v>171900</v>
+        <v>600</v>
       </c>
       <c r="J45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K45" s="3">
         <v>164400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>185000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>183300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>187700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>169900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>155800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>157300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>202400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>149400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>134900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>98100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>128600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>117200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>126400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>124400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>133100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>149600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>129400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>125000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>161700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>118900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>125500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>126500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>142800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>132000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>132700</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>575900</v>
+      </c>
+      <c r="E46" s="3">
         <v>542400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>637300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>710700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>784900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>797600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>804500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>945300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1015300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>964800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>937200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1022800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>987500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>949200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>947100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>990500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1007800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>881700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>967100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1059500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1091700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1015500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>988500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1258600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1148500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1069300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1156400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1291000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1286300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1304800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1280300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1347300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1389600</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4236,47 +4341,47 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>300</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>300</v>
       </c>
       <c r="M47" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="N47" s="3">
         <v>400</v>
       </c>
       <c r="O47" s="3">
+        <v>400</v>
+      </c>
+      <c r="P47" s="3">
         <v>5400</v>
-      </c>
-      <c r="P47" s="3">
-        <v>6800</v>
       </c>
       <c r="Q47" s="3">
         <v>6800</v>
       </c>
       <c r="R47" s="3">
+        <v>6800</v>
+      </c>
+      <c r="S47" s="3">
         <v>59100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>58000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>90400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>67000</v>
-      </c>
-      <c r="V47" s="3">
-        <v>7000</v>
       </c>
       <c r="W47" s="3">
         <v>7000</v>
       </c>
       <c r="X47" s="3">
-        <v>7600</v>
+        <v>7000</v>
       </c>
       <c r="Y47" s="3">
         <v>7600</v>
@@ -4285,7 +4390,7 @@
         <v>7600</v>
       </c>
       <c r="AA47" s="3">
-        <v>1000</v>
+        <v>7600</v>
       </c>
       <c r="AB47" s="3">
         <v>1000</v>
@@ -4297,13 +4402,13 @@
         <v>1000</v>
       </c>
       <c r="AE47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AF47" s="3">
         <v>900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>7400</v>
-      </c>
-      <c r="AG47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH47" s="3" t="s">
         <v>8</v>
@@ -4311,210 +4416,219 @@
       <c r="AI47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>180700</v>
+      </c>
+      <c r="E48" s="3">
         <v>187400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>196700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>208200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>223100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>220800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>225700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>236800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>233800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>249200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>251800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>267400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>280700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>297100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>316800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>340800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>363000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>387200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>407800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>439700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>447100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>470600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>484700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>183200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>190600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>200100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>208500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>219700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>243400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>255800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>260400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>273900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>290800</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E49" s="3">
         <v>10900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>12400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>13000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>13600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>14300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>15000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>15800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>16500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>17800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>19300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>20800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>22400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>26900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>28000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>46400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>48100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>68300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>71300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>74300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>83900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>86700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>89500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>92500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>499800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>502400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>515800</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4614,8 +4728,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4715,109 +4832,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>45000</v>
+        <v>21400</v>
       </c>
       <c r="E52" s="3">
-        <v>45900</v>
+        <v>22000</v>
       </c>
       <c r="F52" s="3">
-        <v>47700</v>
+        <v>22600</v>
       </c>
       <c r="G52" s="3">
-        <v>43700</v>
+        <v>23800</v>
       </c>
       <c r="H52" s="3">
-        <v>43300</v>
+        <v>24200</v>
       </c>
       <c r="I52" s="3">
-        <v>44000</v>
+        <v>23200</v>
       </c>
       <c r="J52" s="3">
+        <v>23500</v>
+      </c>
+      <c r="K52" s="3">
         <v>44100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>53100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>56100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>62300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>63900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>67400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>68600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>61900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>70400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>74300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>71300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>68200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>71700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>66800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>68100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>61100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>57600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>58100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>61600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>65900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>59900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>130100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>115500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>61100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>63400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>61500</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4917,109 +5040,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>812400</v>
+      </c>
+      <c r="E54" s="3">
         <v>785700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>891000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>978000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1063200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1073400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1086000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1238100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1315000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1283400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1265300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1368700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1356000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1337400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1349100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1478500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1522300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1451300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1532600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1604700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1640600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1608200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1589900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1575200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1469500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1406200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1515700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1658400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1750400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1776000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2101700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2186900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>2257600</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5055,8 +5184,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5092,138 +5222,142 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>159000</v>
+      </c>
+      <c r="E57" s="3">
         <v>132500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>142900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>147200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>158000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>139800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>120100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>191100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>204000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>208700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>198500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>229900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>246300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>213500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>201200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>178200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>213100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>127900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>132700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>172200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>193000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>178500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>138300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>169600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>159400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>139500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>133700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>205000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>248800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>163500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>151200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>163600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>193600</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>2600</v>
+        <v>42700</v>
       </c>
       <c r="E58" s="3">
-        <v>500</v>
+        <v>42200</v>
       </c>
       <c r="F58" s="3">
-        <v>500</v>
+        <v>40700</v>
       </c>
       <c r="G58" s="3">
-        <v>500</v>
+        <v>44000</v>
       </c>
       <c r="H58" s="3">
+        <v>44200</v>
+      </c>
+      <c r="I58" s="3">
+        <v>45500</v>
+      </c>
+      <c r="J58" s="3">
+        <v>46100</v>
+      </c>
+      <c r="K58" s="3">
+        <v>300</v>
+      </c>
+      <c r="L58" s="3">
         <v>400</v>
-      </c>
-      <c r="I58" s="3">
-        <v>500</v>
-      </c>
-      <c r="J58" s="3">
-        <v>300</v>
-      </c>
-      <c r="K58" s="3">
-        <v>400</v>
-      </c>
-      <c r="L58" s="3">
-        <v>600</v>
       </c>
       <c r="M58" s="3">
         <v>600</v>
@@ -5232,61 +5366,61 @@
         <v>600</v>
       </c>
       <c r="O58" s="3">
+        <v>600</v>
+      </c>
+      <c r="P58" s="3">
         <v>41200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>38400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>37900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>41600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>21400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>25200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>21100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>26200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>21900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>66400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>65900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>126400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>128000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>127700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>127100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>40200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>32700</v>
-      </c>
-      <c r="AG58" s="3">
-        <v>26400</v>
       </c>
       <c r="AH58" s="3">
         <v>26400</v>
@@ -5294,412 +5428,427 @@
       <c r="AI58" s="3">
         <v>26400</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>26400</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>144600</v>
+        <v>41100</v>
       </c>
       <c r="E59" s="3">
-        <v>152000</v>
+        <v>40300</v>
       </c>
       <c r="F59" s="3">
-        <v>194800</v>
+        <v>49000</v>
       </c>
       <c r="G59" s="3">
-        <v>190100</v>
+        <v>63600</v>
       </c>
       <c r="H59" s="3">
-        <v>181200</v>
+        <v>60000</v>
       </c>
       <c r="I59" s="3">
-        <v>184600</v>
+        <v>50600</v>
       </c>
       <c r="J59" s="3">
+        <v>60800</v>
+      </c>
+      <c r="K59" s="3">
         <v>234400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>224300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>212000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>233500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>305200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>281900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>269900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>268100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>338800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>315400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>310600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>309400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>360800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>314300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>282700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>292400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>309800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>283800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>240300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>263100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>302000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>264500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>217800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>209100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>224600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>204200</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>317500</v>
+      </c>
+      <c r="E60" s="3">
         <v>279700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>295400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>342500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>348600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>321500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>305100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>425900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>428700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>421300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>432700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>535600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>569400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>521800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>507200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>558500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>549900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>463700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>463200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>559200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>529100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>527600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>496500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>605800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>571200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>507500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>523900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>509100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>553500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>414100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>386700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>414600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>424100</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>156500</v>
+        <v>294100</v>
       </c>
       <c r="E61" s="3">
-        <v>202900</v>
+        <v>281900</v>
       </c>
       <c r="F61" s="3">
-        <v>207000</v>
+        <v>332000</v>
       </c>
       <c r="G61" s="3">
-        <v>255900</v>
+        <v>344600</v>
       </c>
       <c r="H61" s="3">
-        <v>243000</v>
+        <v>398100</v>
       </c>
       <c r="I61" s="3">
-        <v>234600</v>
+        <v>378100</v>
       </c>
       <c r="J61" s="3">
+        <v>375400</v>
+      </c>
+      <c r="K61" s="3">
         <v>216100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>293600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>248900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>183900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>141400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>97400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>139700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>157200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>185900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>217900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>243900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>298500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>178800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>242100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>162000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>161100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>269800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>269100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>268400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>335500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>443900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>444300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>613600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>589700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>610000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>697400</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>162400</v>
+        <v>38200</v>
       </c>
       <c r="E62" s="3">
-        <v>166100</v>
+        <v>36400</v>
       </c>
       <c r="F62" s="3">
-        <v>176800</v>
+        <v>36300</v>
       </c>
       <c r="G62" s="3">
-        <v>180000</v>
+        <v>32800</v>
       </c>
       <c r="H62" s="3">
-        <v>171900</v>
+        <v>37200</v>
       </c>
       <c r="I62" s="3">
-        <v>180000</v>
+        <v>36200</v>
       </c>
       <c r="J62" s="3">
+        <v>38600</v>
+      </c>
+      <c r="K62" s="3">
         <v>193100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>202400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>219200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>219300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>226400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>246300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>266600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>275800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>294100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>331000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>347100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>354500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>362900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>359500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>379000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>383000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>111000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>99600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>113500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>129700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>124400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>99600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>93500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>142900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>146900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>151100</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5799,8 +5948,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5900,8 +6052,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6001,109 +6156,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>596000</v>
+        <v>650500</v>
       </c>
       <c r="E66" s="3">
-        <v>661900</v>
+        <v>598600</v>
       </c>
       <c r="F66" s="3">
-        <v>723800</v>
+        <v>664400</v>
       </c>
       <c r="G66" s="3">
-        <v>782100</v>
+        <v>726300</v>
       </c>
       <c r="H66" s="3">
-        <v>733900</v>
+        <v>784500</v>
       </c>
       <c r="I66" s="3">
-        <v>716900</v>
+        <v>736500</v>
       </c>
       <c r="J66" s="3">
+        <v>719700</v>
+      </c>
+      <c r="K66" s="3">
         <v>832200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>921900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>886200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>838200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>905500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>915000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>929600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>941300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1039400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1099500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1055300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1117100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1101700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1131400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1069000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1044200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>989700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>942700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>891200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>994200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1082200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1109100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1132900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1129800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1180700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1284900</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6139,8 +6300,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6240,8 +6402,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6341,8 +6506,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6442,8 +6610,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6543,109 +6714,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-76700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-44700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-5900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>18400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>46600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>107700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>134200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>175500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>184900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>179100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>198100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>229100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>209500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>178100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>179300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>203700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>207700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>191700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>214200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>299800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>306700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>332600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>339900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>381600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>332000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>327000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>334800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>409700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>489500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>494900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>839600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>887800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>838100</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6745,8 +6922,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6846,8 +7026,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6947,109 +7130,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>164400</v>
+      </c>
+      <c r="E76" s="3">
         <v>189600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>229100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>254200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>281100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>339500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>369100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>405900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>393000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>397300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>427200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>463200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>440900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>407900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>407800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>439100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>422800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>396100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>415400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>503100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>509300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>539200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>545700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>585500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>526800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>515000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>521400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>576100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>641300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>643000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>971900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1006200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>972700</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7149,215 +7338,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E80" s="2">
         <v>45472</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45381</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45290</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45108</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45017</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44835</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44744</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44653</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44562</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44471</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44380</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44289</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44198</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44107</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44016</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43925</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43827</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43736</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43645</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43554</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43463</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43372</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43099</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42917</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42826</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-38800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-24300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-28200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-61100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-26500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-41300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-9400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-19100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-21500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>19600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>31400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-24400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>16000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-22500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-85600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-6900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-25900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-7300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-12200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>47600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>5000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-7800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-48300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-79900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-5400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-344700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-48200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>49700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7393,109 +7591,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3900</v>
+        <v>4400</v>
       </c>
       <c r="E83" s="3">
         <v>4500</v>
       </c>
       <c r="F83" s="3">
-        <v>4600</v>
+        <v>4900</v>
       </c>
       <c r="G83" s="3">
-        <v>4600</v>
+        <v>4800</v>
       </c>
       <c r="H83" s="3">
-        <v>4800</v>
+        <v>5000</v>
       </c>
       <c r="I83" s="3">
         <v>5100</v>
       </c>
       <c r="J83" s="3">
+        <v>5600</v>
+      </c>
+      <c r="K83" s="3">
         <v>5700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5800</v>
-      </c>
-      <c r="M83" s="3">
-        <v>6200</v>
       </c>
       <c r="N83" s="3">
         <v>6200</v>
       </c>
       <c r="O83" s="3">
+        <v>6200</v>
+      </c>
+      <c r="P83" s="3">
         <v>7000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>8900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>10000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>10300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>10700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>12200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>12900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>13500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>13900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>14400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>20400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>16100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>15100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>16000</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>19400</v>
       </c>
       <c r="AE83" s="3">
         <v>19400</v>
       </c>
       <c r="AF83" s="3">
+        <v>19400</v>
+      </c>
+      <c r="AG83" s="3">
         <v>21200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>20900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>21400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7595,8 +7797,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7696,8 +7901,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7797,8 +8005,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7898,8 +8109,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7999,109 +8213,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="E89" s="3">
         <v>38400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>48500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-24900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-85900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>103900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-49000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-50700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-115000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>87000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-27200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>28100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-37800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>5400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>84200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>88800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-77100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>124000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-112100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-33700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>7600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>175700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-4900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>81700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>119400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>24800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-16000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>51400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>150800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-12600</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8137,109 +8357,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1700</v>
+        <v>-1300</v>
       </c>
       <c r="E91" s="3">
         <v>-1700</v>
       </c>
       <c r="F91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="G91" s="3">
         <v>-1400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-6800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-6600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-7800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-8300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-4500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-8400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-8800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-12200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-14200</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8339,8 +8563,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8440,109 +8667,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>15100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-7600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>35300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-8500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-4100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-7800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-4300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-7500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>30100</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8578,31 +8811,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8679,8 +8913,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8780,8 +9017,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8881,8 +9121,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8982,307 +9225,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-44800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-49400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>12500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>6800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>16500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-79200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>44000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>56100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>32100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-15100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-41200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-22100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-34200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-14900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-32900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-53700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>112300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-66300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>36300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-172400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-71700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>12000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-45200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-162900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>28500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-22000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-92600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-12300</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>400</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
-        <v>700</v>
+        <v>-2900</v>
       </c>
       <c r="F101" s="3">
+        <v>300</v>
+      </c>
+      <c r="G101" s="3">
+        <v>6600</v>
+      </c>
+      <c r="H101" s="3">
         <v>3200</v>
       </c>
-      <c r="G101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-2900</v>
-      </c>
       <c r="I101" s="3">
-        <v>300</v>
+        <v>-300</v>
       </c>
       <c r="J101" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="K101" s="3">
         <v>6600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1300</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>1000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-6600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>4100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-2600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>12500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>2600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>600</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>4800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>3500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>4700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-10600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>10800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-16200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>4700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-71800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>30400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-88800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>68800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-71300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>6300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-63500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-6800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>46400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>32500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>44500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>52700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-79400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-44600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-131800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>173100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-5800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>11900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>64300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-152900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>23500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>61400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>4100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FOSL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FOSL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
   <si>
     <t>FOSL</t>
   </si>
@@ -656,459 +656,471 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E7" s="2">
         <v>45563</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45472</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45381</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45290</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45108</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45017</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44835</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44744</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44653</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44562</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44471</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44380</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44289</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44198</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44107</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44016</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43925</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43827</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43736</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43645</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43554</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43463</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43372</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43099</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42917</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42826</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>342300</v>
+      </c>
+      <c r="E8" s="3">
         <v>287800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>260000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>254900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>421300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>344100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>322000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>325000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>499100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>436300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>371200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>375900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>604200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>491800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>410900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>363000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>528100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>435500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>259000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>390700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>711600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>539500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>501400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>465300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>786900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>608800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>576600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>569200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>920800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>688700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>596800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>581800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>959200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>738000</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>150200</v>
+      </c>
+      <c r="E9" s="3">
         <v>145600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>123100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>121600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>222000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>183800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>162400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>159100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>263800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>216700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>179800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>191500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>301800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>232300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>189100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>180500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>268500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>205700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>118400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>250400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>403700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>260900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>236300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>217300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>370000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>282300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>267600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>281500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>472700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>368800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>295500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>292300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>470100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>352900</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>192100</v>
+      </c>
+      <c r="E10" s="3">
         <v>142200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>136900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>133300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>199200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>160300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>159600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>166000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>235400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>219600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>191400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>184400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>302400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>259500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>221800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>182500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>259600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>229800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>140600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>140300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>307900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>278600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>265100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>248000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>416900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>326500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>309000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>287700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>448100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>319900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>301300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>289500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>489100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>385100</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1145,8 +1157,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1159,11 +1172,11 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="3">
         <v>19400</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
@@ -1249,8 +1262,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1353,112 +1369,118 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E14" s="3">
         <v>5800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>17300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>10200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>15600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>15300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>7700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>12400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>6100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>6000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>7000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>12000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>17800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>9700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>14100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>28600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>12800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>25100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>9000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>11000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>4800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>6200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>21000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>23500</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>6400</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>5800</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>416900</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>26300</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>13300</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,25 +1488,25 @@
         <v>3800</v>
       </c>
       <c r="E15" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F15" s="3">
         <v>3900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4500</v>
-      </c>
-      <c r="G15" s="3">
-        <v>4600</v>
       </c>
       <c r="H15" s="3">
         <v>4600</v>
       </c>
       <c r="I15" s="3">
+        <v>4600</v>
+      </c>
+      <c r="J15" s="3">
         <v>4800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5100</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>8</v>
@@ -1498,8 +1520,8 @@
       <c r="O15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P15" s="3">
-        <v>100</v>
+      <c r="P15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q15" s="3">
         <v>100</v>
@@ -1529,10 +1551,10 @@
         <v>100</v>
       </c>
       <c r="Z15" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA15" s="3">
         <v>400</v>
-      </c>
-      <c r="AA15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB15" s="3" t="s">
         <v>8</v>
@@ -1543,8 +1565,8 @@
       <c r="AD15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE15" s="3">
-        <v>0</v>
+      <c r="AE15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF15" s="3">
         <v>0</v>
@@ -1561,8 +1583,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1596,216 +1621,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>322200</v>
+      </c>
+      <c r="E17" s="3">
         <v>306400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>276700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>273900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>429700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>375200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>349600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>349900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>497900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>413800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>382100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>390100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>557000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>444000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>396600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>379800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>509800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>418000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>295800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>525100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>715600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>548600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>499700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>485200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>719600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>586200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>575600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>598100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>869600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>689200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1026600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>627100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>893000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>706800</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-18600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-16800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-19000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-8400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-31100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-27600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-24900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>22500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-10900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-14200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>47200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>47800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>14300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-16800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>18300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>17500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-36800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-134400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-4000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-9100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-19900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>67300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>22600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-28900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>51200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-429800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-45300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>66200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>31200</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1842,216 +1874,223 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-7200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-15400</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-500</v>
       </c>
       <c r="Q20" s="3">
         <v>-500</v>
       </c>
       <c r="R20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="S20" s="3">
         <v>1900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1600</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-7300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>5000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>25900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>5300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>3900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>5600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>7600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-11200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-11400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-11800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-5200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-29600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-15600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-17700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>7500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>26300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-6800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-6500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>38100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>54300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>21300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-6000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>29900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>27800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-25200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-129400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>14000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>3000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>16100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>20400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>93100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>35800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>15500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-14200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>72900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>22800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-406600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-18700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>95200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>56300</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2059,311 +2098,320 @@
         <v>4900</v>
       </c>
       <c r="E22" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F22" s="3">
         <v>4100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>5700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>5800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>5300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>5100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>4300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>4000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>4800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>6400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>6500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>7300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>8500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>8000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>7900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>7500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>7000</v>
-      </c>
-      <c r="X22" s="3">
-        <v>7400</v>
       </c>
       <c r="Y22" s="3">
         <v>7400</v>
       </c>
       <c r="Z22" s="3">
+        <v>7400</v>
+      </c>
+      <c r="AA22" s="3">
         <v>8100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>10800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>9900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>11100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>10700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>11100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>12100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>11600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>8400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>7500</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>7000</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-25800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-36600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-30400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-27800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-55200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-33500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-39600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>15500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-16900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-16700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>27100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>40900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>7300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-22200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>11400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>9500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-43800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-149100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-6000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-18000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>61800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>9900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-10600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-40900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>42400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-8700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-439400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-48000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>66300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>25800</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E24" s="3">
         <v>6200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-6100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-7200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>9200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>9000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>8100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>15200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-6800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-20800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-63700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>6900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>9600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>13900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>3900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>6600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>87000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-96300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>15500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2466,216 +2514,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-31900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-38800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-24300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-28400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-60800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-26300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-41200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-18900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-21300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>19800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>31900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-24300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>16200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-23000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-85400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-6700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-24900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-6600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-11800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>47900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>5900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-7200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-47500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-44600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-5500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-343100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-46800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>50800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-32000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-38800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-24300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-28200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-61100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-26500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-41300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-19100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-21500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>19600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>31400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-24400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>16000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-22500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-85600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-6900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-25900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-7300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-12200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>47600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>5000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-7800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-48300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-46300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-5400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-344700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-48200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>49700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2778,8 +2835,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2846,8 +2906,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2864,11 +2924,11 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-33600</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -2882,8 +2942,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2986,8 +3049,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3090,216 +3156,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E32" s="3">
         <v>3600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>7200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>15400</v>
-      </c>
-      <c r="P32" s="3">
-        <v>500</v>
       </c>
       <c r="Q32" s="3">
         <v>500</v>
       </c>
       <c r="R32" s="3">
+        <v>500</v>
+      </c>
+      <c r="S32" s="3">
         <v>-1900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1600</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>7300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-5000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-25900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-5300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-5600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-7600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-32000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-38800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-24300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-28200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-61100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-26500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-41300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-19100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-21500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>19600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>31400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-24400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>16000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-22500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-85600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-6900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-25900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-7300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-12200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>47600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>5000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-7800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-48300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-79900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-5400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-344700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-48200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>49700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3402,221 +3477,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-32000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-38800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-24300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-28200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-61100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-26500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-41300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-19100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-21500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>19600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>31400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-24400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>16000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-22500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-85600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-6900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-25900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-7300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-12200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>47600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>5000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-7800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-48300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-79900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-5400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-344700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-48200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>49700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E38" s="2">
         <v>45563</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45472</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45381</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45290</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45108</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45017</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44835</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44744</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44653</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44562</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44471</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44380</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44289</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44198</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44107</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44016</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43925</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43827</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43736</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43645</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43554</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43463</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43372</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43099</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42917</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42826</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3653,8 +3737,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3691,117 +3776,121 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>123600</v>
+      </c>
+      <c r="E41" s="3">
         <v>106300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>104900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>112900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>117200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>116100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>132100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>127100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>198700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>162600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>167100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>162600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>250800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>181800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>252300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>246700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>316000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>323600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>277600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>245400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>200200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>147500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>226600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>271400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>403400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>236100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>241800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>229900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>231200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>166900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>319800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>320700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>297300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>236000</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -3810,11 +3899,11 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>600</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -3899,424 +3988,439 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>185600</v>
+      </c>
+      <c r="E43" s="3">
         <v>173700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>133100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>134400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
+        <v>268900</v>
+      </c>
+      <c r="I43" s="3">
+        <v>194000</v>
+      </c>
+      <c r="J43" s="3">
+        <v>162700</v>
+      </c>
+      <c r="K43" s="3">
+        <v>168900</v>
+      </c>
+      <c r="L43" s="3">
+        <v>206100</v>
+      </c>
+      <c r="M43" s="3">
+        <v>215000</v>
+      </c>
+      <c r="N43" s="3">
+        <v>176500</v>
+      </c>
+      <c r="O43" s="3">
+        <v>201100</v>
+      </c>
+      <c r="P43" s="3">
+        <v>255100</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>251500</v>
+      </c>
+      <c r="R43" s="3">
+        <v>187600</v>
+      </c>
+      <c r="S43" s="3">
+        <v>175500</v>
+      </c>
+      <c r="T43" s="3">
+        <v>229800</v>
+      </c>
+      <c r="U43" s="3">
+        <v>189800</v>
+      </c>
+      <c r="V43" s="3">
+        <v>130100</v>
+      </c>
+      <c r="W43" s="3">
+        <v>153400</v>
+      </c>
+      <c r="X43" s="3">
+        <v>289700</v>
+      </c>
+      <c r="Y43" s="3">
+        <v>247600</v>
+      </c>
+      <c r="Z43" s="3">
+        <v>204200</v>
+      </c>
+      <c r="AA43" s="3">
+        <v>199900</v>
+      </c>
+      <c r="AB43" s="3">
+        <v>328000</v>
+      </c>
+      <c r="AC43" s="3">
+        <v>261700</v>
+      </c>
+      <c r="AD43" s="3">
+        <v>204700</v>
+      </c>
+      <c r="AE43" s="3">
+        <v>234200</v>
+      </c>
+      <c r="AF43" s="3">
+        <v>367000</v>
+      </c>
+      <c r="AG43" s="3">
+        <v>310900</v>
+      </c>
+      <c r="AH43" s="3">
+        <v>240400</v>
+      </c>
+      <c r="AI43" s="3">
         <v>245300</v>
       </c>
-      <c r="H43" s="3">
-        <v>194000</v>
-      </c>
-      <c r="I43" s="3">
-        <v>162700</v>
-      </c>
-      <c r="J43" s="3">
-        <v>168900</v>
-      </c>
-      <c r="K43" s="3">
-        <v>206100</v>
-      </c>
-      <c r="L43" s="3">
-        <v>215000</v>
-      </c>
-      <c r="M43" s="3">
-        <v>176500</v>
-      </c>
-      <c r="N43" s="3">
-        <v>201100</v>
-      </c>
-      <c r="O43" s="3">
-        <v>255100</v>
-      </c>
-      <c r="P43" s="3">
-        <v>251500</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>187600</v>
-      </c>
-      <c r="R43" s="3">
-        <v>175500</v>
-      </c>
-      <c r="S43" s="3">
-        <v>229800</v>
-      </c>
-      <c r="T43" s="3">
-        <v>189800</v>
-      </c>
-      <c r="U43" s="3">
-        <v>130100</v>
-      </c>
-      <c r="V43" s="3">
-        <v>153400</v>
-      </c>
-      <c r="W43" s="3">
-        <v>289700</v>
-      </c>
-      <c r="X43" s="3">
-        <v>247600</v>
-      </c>
-      <c r="Y43" s="3">
-        <v>204200</v>
-      </c>
-      <c r="Z43" s="3">
-        <v>199900</v>
-      </c>
-      <c r="AA43" s="3">
-        <v>328000</v>
-      </c>
-      <c r="AB43" s="3">
-        <v>261700</v>
-      </c>
-      <c r="AC43" s="3">
-        <v>204700</v>
-      </c>
-      <c r="AD43" s="3">
-        <v>234200</v>
-      </c>
-      <c r="AE43" s="3">
-        <v>367000</v>
-      </c>
-      <c r="AF43" s="3">
-        <v>310900</v>
-      </c>
-      <c r="AG43" s="3">
-        <v>240400</v>
-      </c>
-      <c r="AH43" s="3">
-        <v>245300</v>
-      </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>375500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>321300</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>178600</v>
+      </c>
+      <c r="E44" s="3">
         <v>226400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>202100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>224100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>252800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>326700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>323900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>336500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>376000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>452700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>437900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>385800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>346900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>398300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>352000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>322500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>295300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>359500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>375900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>439700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>452300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>570300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>460300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>384100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>377600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>521300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>497800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>530700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>573800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>683000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>618100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>571500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>542500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>699600</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E45" s="3">
         <v>100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1300</v>
       </c>
-      <c r="G45" s="3">
-        <v>42800</v>
-      </c>
       <c r="H45" s="3">
+        <v>19200</v>
+      </c>
+      <c r="I45" s="3">
         <v>3800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>164400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>185000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>183300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>187700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>169900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>155800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>157300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>202400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>149400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>134900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>98100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>128600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>117200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>126400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>124400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>133100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>149600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>129400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>125000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>161700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>118900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>125500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>126500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>142800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>132000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>132700</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>554500</v>
+      </c>
+      <c r="E46" s="3">
         <v>575900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>542400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>637300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>710700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>784900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>797600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>804500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>945300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1015300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>964800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>937200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1022800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>987500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>949200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>947100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>990500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1007800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>881700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>967100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1059500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1091700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1015500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>988500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1258600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1148500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1069300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1156400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1291000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1286300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1304800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1280300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1347300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1389600</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4344,47 +4448,47 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>300</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>300</v>
       </c>
       <c r="N47" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="O47" s="3">
         <v>400</v>
       </c>
       <c r="P47" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q47" s="3">
         <v>5400</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>6800</v>
       </c>
       <c r="R47" s="3">
         <v>6800</v>
       </c>
       <c r="S47" s="3">
+        <v>6800</v>
+      </c>
+      <c r="T47" s="3">
         <v>59100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>58000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>90400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>67000</v>
-      </c>
-      <c r="W47" s="3">
-        <v>7000</v>
       </c>
       <c r="X47" s="3">
         <v>7000</v>
       </c>
       <c r="Y47" s="3">
-        <v>7600</v>
+        <v>7000</v>
       </c>
       <c r="Z47" s="3">
         <v>7600</v>
@@ -4393,7 +4497,7 @@
         <v>7600</v>
       </c>
       <c r="AB47" s="3">
-        <v>1000</v>
+        <v>7600</v>
       </c>
       <c r="AC47" s="3">
         <v>1000</v>
@@ -4405,13 +4509,13 @@
         <v>1000</v>
       </c>
       <c r="AF47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AG47" s="3">
         <v>900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>7400</v>
-      </c>
-      <c r="AH47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI47" s="3" t="s">
         <v>8</v>
@@ -4419,216 +4523,225 @@
       <c r="AJ47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>163000</v>
+      </c>
+      <c r="E48" s="3">
         <v>180700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>187400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>196700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>208200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>223100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>220800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>225700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>236800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>233800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>249200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>251800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>267400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>280700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>297100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>316800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>340800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>363000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>387200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>407800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>439700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>447100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>470600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>484700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>183200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>190600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>200100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>208500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>219700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>243400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>255800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>260400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>273900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>290800</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E49" s="3">
         <v>10700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>12400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>13000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>13600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>14300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>15000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>15800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>16500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>17800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>19300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>20800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>22400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>26900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>28000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>46400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>48100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>68300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>71300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>74300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>83900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>86700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>89500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>92500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>499800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>502400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>515800</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4731,8 +4844,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4835,112 +4951,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E52" s="3">
         <v>21400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>22000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>22600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>23800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>24200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>23200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>23500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>44100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>53100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>56100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>62300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>63900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>67400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>68600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>61900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>70400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>74300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>71300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>68200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>71700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>66800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>68100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>61100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>57600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>58100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>61600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>65900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>59900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>130100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>115500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>61100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>63400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>61500</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5043,112 +5165,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>763600</v>
+      </c>
+      <c r="E54" s="3">
         <v>812400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>785700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>891000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>978000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1063200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1073400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1086000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1238100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1315000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1283400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1265300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1368700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1356000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1337400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1349100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1478500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1522300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1451300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1532600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1604700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1640600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1608200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1589900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1575200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1469500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1406200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1515700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1658400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1750400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1776000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2101700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>2186900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>2257600</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5185,8 +5313,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5223,144 +5352,148 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>157600</v>
+      </c>
+      <c r="E57" s="3">
         <v>159000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>132500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>142900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>147200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>158000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>139800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>120100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>191100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>204000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>208700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>198500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>229900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>246300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>213500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>201200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>178200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>213100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>127900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>132700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>172200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>193000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>178500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>138300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>169600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>159400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>139500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>133700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>205000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>248800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>163500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>151200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>163600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>193600</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E58" s="3">
         <v>42700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>42200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>40700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>44000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>44200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>45500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>46100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>400</v>
-      </c>
-      <c r="M58" s="3">
-        <v>600</v>
       </c>
       <c r="N58" s="3">
         <v>600</v>
@@ -5369,61 +5502,61 @@
         <v>600</v>
       </c>
       <c r="P58" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q58" s="3">
         <v>41200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>38400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>37900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>41600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>21400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>25200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>21100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>26200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>21900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>66400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>65900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>126400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>128000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>127700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>127100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>40200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>32700</v>
-      </c>
-      <c r="AH58" s="3">
-        <v>26400</v>
       </c>
       <c r="AI58" s="3">
         <v>26400</v>
@@ -5431,424 +5564,439 @@
       <c r="AJ58" s="3">
         <v>26400</v>
       </c>
+      <c r="AK58" s="3">
+        <v>26400</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>43700</v>
+      </c>
+      <c r="E59" s="3">
         <v>41100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>40300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>49000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>63600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>60000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>50600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>60800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>234400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>224300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>212000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>233500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>305200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>281900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>269900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>268100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>338800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>315400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>310600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>309400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>360800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>314300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>282700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>292400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>309800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>283800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>240300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>263100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>302000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>264500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>217800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>209100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>224600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>204200</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>326600</v>
+      </c>
+      <c r="E60" s="3">
         <v>317500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>279700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>295400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>342500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>348600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>321500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>305100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>425900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>428700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>421300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>432700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>535600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>569400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>521800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>507200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>558500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>549900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>463700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>463200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>559200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>529100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>527600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>496500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>605800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>571200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>507500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>523900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>509100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>553500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>414100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>386700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>414600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>424100</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>276300</v>
+      </c>
+      <c r="E61" s="3">
         <v>294100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>281900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>332000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>344600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>398100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>378100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>375400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>216100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>293600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>248900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>183900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>141400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>97400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>139700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>157200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>185900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>217900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>243900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>298500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>178800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>242100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>162000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>161100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>269800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>269100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>268400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>335500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>443900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>444300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>613600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>589700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>610000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>697400</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E62" s="3">
         <v>38200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>36400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>36300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>32800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>37200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>36200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>38600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>193100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>202400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>219200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>219300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>226400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>246300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>266600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>275800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>294100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>331000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>347100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>354500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>362900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>359500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>379000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>383000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>111000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>99600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>113500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>129700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>124400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>99600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>93500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>142900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>146900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>151100</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5951,8 +6099,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6055,8 +6206,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6159,112 +6313,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>626800</v>
+      </c>
+      <c r="E66" s="3">
         <v>650500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>598600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>664400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>726300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>784500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>736500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>719700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>832200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>921900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>886200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>838200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>905500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>915000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>929600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>941300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1039400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1099500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1055300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1117100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1101700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1131400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1069000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1044200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>989700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>942700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>891200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>994200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1082200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1109100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1132900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1129800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1180700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1284900</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6301,8 +6461,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6405,8 +6566,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6509,8 +6673,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6613,8 +6780,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6717,112 +6887,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-84300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-76700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-44700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-5900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>18400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>46600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>107700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>134200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>175500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>184900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>179100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>198100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>229100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>209500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>178100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>179300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>203700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>207700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>191700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>214200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>299800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>306700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>332600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>339900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>381600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>332000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>327000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>334800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>409700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>489500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>494900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>839600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>887800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>838100</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6925,8 +7101,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7029,8 +7208,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7133,112 +7315,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>148700</v>
+      </c>
+      <c r="E76" s="3">
         <v>164400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>189600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>229100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>254200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>281100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>339500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>369100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>405900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>393000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>397300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>427200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>463200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>440900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>407900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>407800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>439100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>422800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>396100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>415400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>503100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>509300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>539200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>545700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>585500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>526800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>515000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>521400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>576100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>641300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>643000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>971900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1006200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>972700</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7341,221 +7529,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E80" s="2">
         <v>45563</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45472</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45381</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45290</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45108</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45017</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44835</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44744</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44653</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44562</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44471</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44380</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44289</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44198</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44107</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44016</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43925</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43827</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43736</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43645</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43554</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43463</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43372</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43099</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42917</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42826</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-32000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-38800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-24300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-28200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-61100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-26500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-41300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-19100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-21500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>19600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>31400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-24400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>16000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-22500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-85600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-6900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-25900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-7300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-12200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>47600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>5000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-7800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-48300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-79900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-5400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-344700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-48200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>49700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7592,112 +7789,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E83" s="3">
         <v>4400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5800</v>
-      </c>
-      <c r="N83" s="3">
-        <v>6200</v>
       </c>
       <c r="O83" s="3">
         <v>6200</v>
       </c>
       <c r="P83" s="3">
+        <v>6200</v>
+      </c>
+      <c r="Q83" s="3">
         <v>7000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>8900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>10000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>10300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>10700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>12200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>12900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>13500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>13900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>14400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>20400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>16100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>15100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>16000</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>19400</v>
       </c>
       <c r="AF83" s="3">
         <v>19400</v>
       </c>
       <c r="AG83" s="3">
+        <v>19400</v>
+      </c>
+      <c r="AH83" s="3">
         <v>21200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>20900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>21400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7800,8 +8001,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7904,8 +8108,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8008,8 +8215,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8112,8 +8322,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8216,112 +8429,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-22800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>38400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>48500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-24900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-85900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>103900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-49000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-50700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-115000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>87000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-27200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>28100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-37800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>5400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>84200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>88800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-77100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>124000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-112100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-33700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>7600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>175700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-4900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>81700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-4300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>119400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>24800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-16000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>51400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>150800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-12600</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8358,112 +8577,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1300</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-1700</v>
       </c>
       <c r="F91" s="3">
         <v>-1700</v>
       </c>
       <c r="G91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="H91" s="3">
         <v>-1400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-6800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-6600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-7800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-3800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-8300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-4500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-8400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-8800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-12200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-14200</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8566,8 +8789,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8670,112 +8896,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
         <v>7200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>15100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-7600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>35300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-8500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-4100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-7800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-4300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-7500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>30100</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8812,8 +9044,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8838,8 +9071,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8916,8 +9149,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9020,8 +9256,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9124,8 +9363,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9228,316 +9470,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="E100" s="3">
         <v>15700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-44800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-49400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>12500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>6800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>16500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-79200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>44000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>56100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>32100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-15100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-41200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-22100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-34200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-14900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-32900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-53700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>112300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-66300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>36300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-6100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-172400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-71700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>12000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-45200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-162900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>28500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-22000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-92600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-12300</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>6600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>3200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>6600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1300</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>1000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-6600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>4100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-2600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>12500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>2600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>600</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>4800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>3500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>4700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-10600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>10800</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E102" s="3">
         <v>1700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-7800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-16200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>4700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-71800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>30400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-88800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>68800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-71300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>6300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-63500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-6800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>46400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>32500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>44500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>52700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-79400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-44600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-131800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>173100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-5800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>11900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>64300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-152900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>23500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>61400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>4100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FOSL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FOSL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
   <si>
     <t>FOSL</t>
   </si>
@@ -656,471 +656,484 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45752</v>
+      </c>
+      <c r="E7" s="2">
         <v>45654</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45563</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45472</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45381</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45290</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45108</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45017</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44835</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44744</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44653</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44562</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44471</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44380</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44289</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44198</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44107</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44016</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43925</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43827</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43736</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43645</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43554</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43463</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43372</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43099</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42917</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>233300</v>
+      </c>
+      <c r="E8" s="3">
         <v>342300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>287800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>260000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>254900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>421300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>344100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>322000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>325000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>499100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>436300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>371200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>375900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>604200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>491800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>410900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>363000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>528100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>435500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>259000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>390700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>711600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>539500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>501400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>465300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>786900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>608800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>576600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>569200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>920800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>688700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>596800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>581800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>959200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>738000</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>90300</v>
+      </c>
+      <c r="E9" s="3">
         <v>150200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>145600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>123100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>121600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>222000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>183800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>162400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>159100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>263800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>216700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>179800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>191500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>301800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>232300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>189100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>180500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>268500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>205700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>118400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>250400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>403700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>260900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>236300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>217300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>370000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>282300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>267600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>281500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>472700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>368800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>295500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>292300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>470100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>352900</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>143000</v>
+      </c>
+      <c r="E10" s="3">
         <v>192100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>142200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>136900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>133300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>199200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>160300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>159600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>166000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>235400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>219600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>191400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>184400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>302400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>259500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>221800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>182500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>259600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>229800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>140600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>140300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>307900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>278600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>265100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>248000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>416900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>326500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>309000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>287700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>448100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>319900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>301300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>289500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>489100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>385100</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1158,8 +1171,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1175,11 +1189,11 @@
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
         <v>19400</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
@@ -1265,8 +1279,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1372,144 +1389,150 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E14" s="3">
         <v>36400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>5800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>17300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>10200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>15600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>15300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>7700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>12400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>6100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>6000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>7000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>12000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>17800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>9700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>14100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>28600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>12800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>25100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>9000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>11000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>4800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>6200</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>21000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>23500</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>6400</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>5800</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>416900</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>26300</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>13300</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>3800</v>
+        <v>3400</v>
       </c>
       <c r="E15" s="3">
         <v>3800</v>
       </c>
       <c r="F15" s="3">
+        <v>3800</v>
+      </c>
+      <c r="G15" s="3">
         <v>3900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4500</v>
-      </c>
-      <c r="H15" s="3">
-        <v>4600</v>
       </c>
       <c r="I15" s="3">
         <v>4600</v>
       </c>
       <c r="J15" s="3">
+        <v>4600</v>
+      </c>
+      <c r="K15" s="3">
         <v>4800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5100</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>8</v>
@@ -1523,8 +1546,8 @@
       <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q15" s="3">
-        <v>100</v>
+      <c r="Q15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R15" s="3">
         <v>100</v>
@@ -1554,10 +1577,10 @@
         <v>100</v>
       </c>
       <c r="AA15" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB15" s="3">
         <v>400</v>
-      </c>
-      <c r="AB15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC15" s="3" t="s">
         <v>8</v>
@@ -1568,8 +1591,8 @@
       <c r="AE15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF15" s="3">
-        <v>0</v>
+      <c r="AF15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG15" s="3">
         <v>0</v>
@@ -1586,8 +1609,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1622,222 +1648,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>224100</v>
+      </c>
+      <c r="E17" s="3">
         <v>322200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>306400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>276700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>273900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>429700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>375200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>349600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>349900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>497900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>413800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>382100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>390100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>557000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>444000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>396600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>379800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>509800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>418000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>295800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>525100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>715600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>548600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>499700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>485200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>719600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>586200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>575600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>598100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>869600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>689200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1026600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>627100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>893000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>706800</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E18" s="3">
         <v>20100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-18600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-16800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-19000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-8400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-31100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-27600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-24900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>22500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-10900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-14200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>47200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>47800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>14300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-16800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>18300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>17500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-36800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-134400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-9100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-19900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>67300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>22600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-28900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>51200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-429800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-45300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>66200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>31200</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1875,543 +1908,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E20" s="3">
         <v>8500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-7200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-15400</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-500</v>
       </c>
       <c r="R20" s="3">
         <v>-500</v>
       </c>
       <c r="S20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="T20" s="3">
         <v>1900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1600</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-7300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>5000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>25900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>5300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>3900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>2000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>5600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>7600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E21" s="3">
         <v>15400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-11200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-11400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-11800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-5200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-29600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-15600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-17700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>26300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-6800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-6500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>38100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>54300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>21300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-6000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>29900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>27800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-25200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-129400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>14000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>3000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>16100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>20400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>93100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>35800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>15500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-14200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>72900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>22800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-406600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-18700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>95200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>56300</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>4900</v>
+        <v>4500</v>
       </c>
       <c r="E22" s="3">
         <v>4900</v>
       </c>
       <c r="F22" s="3">
+        <v>4900</v>
+      </c>
+      <c r="G22" s="3">
         <v>4100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>5100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>5700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>5800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>5800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>5100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>4300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>4000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>4800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>6400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>6500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>7300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>8500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>8000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>7900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>7500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>7000</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>7400</v>
       </c>
       <c r="Z22" s="3">
         <v>7400</v>
       </c>
       <c r="AA22" s="3">
+        <v>7400</v>
+      </c>
+      <c r="AB22" s="3">
         <v>8100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>10800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>9900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>11100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>10700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>11100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>12100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>11600</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>8400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>7500</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>7000</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-14500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-25200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-25800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-36600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-30400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-27800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-55200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-33500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-39600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>15500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-16900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-16700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>27100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>40900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-22200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>11400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>9500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-43800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-149100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-18000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>61800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>9900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-10600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-40900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>42400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-8700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-439400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-48000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>66300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>25800</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-14000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-6100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-7200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>7300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>9000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>8100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>15200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-6800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-20800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-63700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>6900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>9600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>13900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>6600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>87000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-96300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>15500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2517,222 +2566,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-11200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-31900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-38800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-24300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-28400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-60800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-26300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-41200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-18900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-21300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>19800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>31900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-24300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>16200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-23000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-85400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-24900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-6600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-11800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>47900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>5900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-7200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-47500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-44600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-5500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-343100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-46800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>50800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-7600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-32000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-38800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-24300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-28200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-61100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-26500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-41300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-19100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-21500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>19600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>31400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-24400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-4000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>16000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-22500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-85600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-25900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-7300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-12200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>47600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>5000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-7800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-48300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-46300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-5400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-344700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-48200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>49700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2838,8 +2896,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2909,8 +2970,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2927,11 +2988,11 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-33600</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -2945,8 +3006,11 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3052,8 +3116,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3159,222 +3226,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-8500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>7200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>15400</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>500</v>
       </c>
       <c r="R32" s="3">
         <v>500</v>
       </c>
       <c r="S32" s="3">
+        <v>500</v>
+      </c>
+      <c r="T32" s="3">
         <v>-1900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1600</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>7300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-25900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-5300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-3900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-5600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-7600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-7600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-32000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-38800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-24300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-28200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-61100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-26500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-41300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-19100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-21500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>19600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>31400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-24400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-4000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>16000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-22500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-85600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-25900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-7300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-12200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>47600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>5000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-7800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-48300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-79900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-5400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-344700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-48200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>49700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3480,227 +3556,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-7600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-32000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-38800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-24300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-28200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-61100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-26500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-41300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-19100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-21500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>19600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>31400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-24400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-4000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>16000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-22500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-85600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-25900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-7300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-12200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>47600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>5000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-7800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-48300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-79900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-5400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-344700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-48200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>49700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45752</v>
+      </c>
+      <c r="E38" s="2">
         <v>45654</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45563</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45472</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45381</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45290</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45108</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45017</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44835</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44744</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44653</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44562</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44471</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44380</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44289</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44198</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44107</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44016</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43925</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43827</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43736</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43645</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43554</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43463</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43372</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43099</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42917</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3738,8 +3823,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3777,124 +3863,128 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>78300</v>
+      </c>
+      <c r="E41" s="3">
         <v>123600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>106300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>104900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>112900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>117200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>116100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>132100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>127100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>198700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>162600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>167100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>162600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>250800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>181800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>252300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>246700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>316000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>323600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>277600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>245400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>200200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>147500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>226600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>271400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>403400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>236100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>241800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>229900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>231200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>166900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>319800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>320700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>297300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>236000</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>1600</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
@@ -3902,11 +3992,11 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>600</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -3991,436 +4081,451 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>124600</v>
+      </c>
+      <c r="E43" s="3">
         <v>185600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>173700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>133100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>134400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>268900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>194000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>162700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>168900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>206100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>215000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>176500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>201100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>255100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>251500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>187600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>175500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>229800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>189800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>130100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>153400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>289700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>247600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>204200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>199900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>328000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>261700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>204700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>234200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>367000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>310900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>240400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>245300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>375500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>321300</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>182100</v>
+      </c>
+      <c r="E44" s="3">
         <v>178600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>226400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>202100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>224100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>252800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>326700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>323900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>336500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>376000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>452700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>437900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>385800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>346900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>398300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>352000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>322500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>295300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>359500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>375900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>439700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>452300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>570300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>460300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>384100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>377600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>521300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>497800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>530700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>573800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>683000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>618100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>571500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>542500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>699600</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>24600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>19200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>164400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>185000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>183300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>187700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>169900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>155800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>157300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>202400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>149400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>134900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>98100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>128600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>117200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>126400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>124400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>133100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>149600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>129400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>125000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>161700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>118900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>125500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>126500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>142800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>132000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>132700</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>482500</v>
+      </c>
+      <c r="E46" s="3">
         <v>554500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>575900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>542400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>637300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>710700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>784900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>797600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>804500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>945300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1015300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>964800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>937200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1022800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>987500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>949200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>947100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>990500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1007800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>881700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>967100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1059500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1091700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1015500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>988500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1258600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1148500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1069300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1156400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1291000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1286300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1304800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1280300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1347300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1389600</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4451,47 +4556,47 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>300</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>300</v>
       </c>
       <c r="O47" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="P47" s="3">
         <v>400</v>
       </c>
       <c r="Q47" s="3">
+        <v>400</v>
+      </c>
+      <c r="R47" s="3">
         <v>5400</v>
-      </c>
-      <c r="R47" s="3">
-        <v>6800</v>
       </c>
       <c r="S47" s="3">
         <v>6800</v>
       </c>
       <c r="T47" s="3">
+        <v>6800</v>
+      </c>
+      <c r="U47" s="3">
         <v>59100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>58000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>90400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>67000</v>
-      </c>
-      <c r="X47" s="3">
-        <v>7000</v>
       </c>
       <c r="Y47" s="3">
         <v>7000</v>
       </c>
       <c r="Z47" s="3">
-        <v>7600</v>
+        <v>7000</v>
       </c>
       <c r="AA47" s="3">
         <v>7600</v>
@@ -4500,7 +4605,7 @@
         <v>7600</v>
       </c>
       <c r="AC47" s="3">
-        <v>1000</v>
+        <v>7600</v>
       </c>
       <c r="AD47" s="3">
         <v>1000</v>
@@ -4512,13 +4617,13 @@
         <v>1000</v>
       </c>
       <c r="AG47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AH47" s="3">
         <v>900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>7400</v>
-      </c>
-      <c r="AI47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AJ47" s="3" t="s">
         <v>8</v>
@@ -4526,222 +4631,231 @@
       <c r="AK47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>157500</v>
+      </c>
+      <c r="E48" s="3">
         <v>163000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>180700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>187400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>196700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>208200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>223100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>220800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>225700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>236800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>233800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>249200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>251800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>267400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>280700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>297100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>316800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>340800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>363000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>387200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>407800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>439700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>447100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>470600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>484700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>183200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>190600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>200100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>208500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>219700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>243400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>255800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>260400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>273900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>290800</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>12400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>13000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>13600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>14300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>15000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>15800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>16500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>17800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>19300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>20800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>22400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>26900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>28000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>46400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>48100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>68300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>71300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>74300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>83900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>86700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>89500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>92500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>499800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>502400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>515800</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4847,8 +4961,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4954,115 +5071,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3">
         <v>19400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>21400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>22000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>22600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>23800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>24200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>23200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>23500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>44100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>53100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>56100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>62300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>63900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>67400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>68600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>61900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>70400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>74300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>71300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>68200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>71700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>66800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>68100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>61100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>57600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>58100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>61600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>65900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>59900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>130100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>115500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>61100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>63400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>61500</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5168,115 +5291,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>686000</v>
+      </c>
+      <c r="E54" s="3">
         <v>763600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>812400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>785700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>891000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>978000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1063200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1073400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1086000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1238100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1315000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1283400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1265300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1368700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1356000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1337400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1349100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1478500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1522300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1451300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1532600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1604700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1640600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1608200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1589900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1575200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1469500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1406200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1515700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1658400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1750400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1776000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>2101700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>2186900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>2257600</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5314,8 +5443,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5353,150 +5483,154 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>118200</v>
+      </c>
+      <c r="E57" s="3">
         <v>157600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>159000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>132500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>142900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>147200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>158000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>139800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>120100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>191100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>204000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>208700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>198500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>229900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>246300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>213500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>201200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>178200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>213100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>127900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>132700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>172200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>193000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>178500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>138300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>169600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>159400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>139500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>133700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>205000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>248800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>163500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>151200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>163600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>193600</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>45300</v>
+      </c>
+      <c r="E58" s="3">
         <v>39500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>42700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>42200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>40700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>44000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>44200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>45500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>46100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>400</v>
-      </c>
-      <c r="N58" s="3">
-        <v>600</v>
       </c>
       <c r="O58" s="3">
         <v>600</v>
@@ -5505,61 +5639,61 @@
         <v>600</v>
       </c>
       <c r="Q58" s="3">
+        <v>600</v>
+      </c>
+      <c r="R58" s="3">
         <v>41200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>38400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>37900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>41600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>21400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>25200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>21100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>26200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>21900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>66400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>65900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>126400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>128000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>127700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>127100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>40200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>32700</v>
-      </c>
-      <c r="AI58" s="3">
-        <v>26400</v>
       </c>
       <c r="AJ58" s="3">
         <v>26400</v>
@@ -5567,436 +5701,451 @@
       <c r="AK58" s="3">
         <v>26400</v>
       </c>
+      <c r="AL58" s="3">
+        <v>26400</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>34900</v>
+      </c>
+      <c r="E59" s="3">
         <v>43700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>41100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>40300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>49000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>63600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>60000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>50600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>60800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>234400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>224300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>212000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>233500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>305200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>281900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>269900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>268100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>338800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>315400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>310600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>309400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>360800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>314300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>282700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>292400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>309800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>283800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>240300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>263100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>302000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>264500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>217800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>209100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>224600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>204200</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>262600</v>
+      </c>
+      <c r="E60" s="3">
         <v>326600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>317500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>279700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>295400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>342500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>348600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>321500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>305100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>425900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>428700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>421300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>432700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>535600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>569400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>521800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>507200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>558500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>549900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>463700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>463200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>559200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>529100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>527600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>496500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>605800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>571200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>507500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>523900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>509100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>553500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>414100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>386700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>414600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>424100</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>276900</v>
+      </c>
+      <c r="E61" s="3">
         <v>276300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>294100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>281900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>332000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>344600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>398100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>378100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>375400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>216100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>293600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>248900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>183900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>141400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>97400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>139700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>157200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>185900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>217900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>243900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>298500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>178800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>242100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>162000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>161100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>269800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>269100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>268400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>335500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>443900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>444300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>613600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>589700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>610000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>697400</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E62" s="3">
         <v>16700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>38200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>36400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>36300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>32800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>37200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>36200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>38600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>193100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>202400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>219200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>219300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>226400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>246300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>266600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>275800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>294100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>331000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>347100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>354500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>362900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>359500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>379000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>383000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>111000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>99600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>113500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>129700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>124400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>99600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>93500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>142900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>146900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>151100</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6102,8 +6251,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6209,8 +6361,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6316,115 +6471,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>561600</v>
+      </c>
+      <c r="E66" s="3">
         <v>626800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>650500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>598600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>664400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>726300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>784500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>736500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>719700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>832200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>921900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>886200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>838200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>905500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>915000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>929600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>941300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1039400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1099500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1055300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1117100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1101700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1131400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1069000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1044200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>989700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>942700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>891200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>994200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1082200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1109100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1132900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1129800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1180700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1284900</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6462,8 +6623,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6569,8 +6731,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6676,8 +6841,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6783,8 +6951,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6890,115 +7061,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-101800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-84300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-76700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-44700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-5900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>18400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>46600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>107700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>134200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>175500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>184900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>179100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>198100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>229100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>209500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>178100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>179300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>203700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>207700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>191700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>214200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>299800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>306700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>332600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>339900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>381600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>332000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>327000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>334800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>409700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>489500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>494900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>839600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>887800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>838100</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7104,8 +7281,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7211,8 +7391,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7318,115 +7501,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>140600</v>
+      </c>
+      <c r="E76" s="3">
         <v>148700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>164400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>189600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>229100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>254200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>281100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>339500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>369100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>405900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>393000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>397300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>427200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>463200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>440900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>407900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>407800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>439100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>422800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>396100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>415400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>503100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>509300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>539200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>545700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>585500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>526800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>515000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>521400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>576100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>641300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>643000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>971900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1006200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>972700</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7532,227 +7721,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45752</v>
+      </c>
+      <c r="E80" s="2">
         <v>45654</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45563</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45472</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45381</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45290</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45108</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45017</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44835</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44744</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44653</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44562</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44471</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44380</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44289</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44198</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44107</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44016</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43925</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43827</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43736</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43645</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43554</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43463</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43372</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43099</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42917</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-7600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-32000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-38800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-24300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-28200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-61100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-26500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-41300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-19100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-21500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>19600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>31400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-24400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-4000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>16000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-22500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-85600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-25900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-7300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-12200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>47600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>5000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-7800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-48300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-79900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-5400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-344700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-48200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>49700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7790,115 +7988,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E83" s="3">
         <v>4100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5800</v>
-      </c>
-      <c r="O83" s="3">
-        <v>6200</v>
       </c>
       <c r="P83" s="3">
         <v>6200</v>
       </c>
       <c r="Q83" s="3">
+        <v>6200</v>
+      </c>
+      <c r="R83" s="3">
         <v>7000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>8900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>10000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>10300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>10700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>12200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>12900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>13500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>13900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>14400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>20400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>16100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>15100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>16000</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>19400</v>
       </c>
       <c r="AG83" s="3">
         <v>19400</v>
       </c>
       <c r="AH83" s="3">
+        <v>19400</v>
+      </c>
+      <c r="AI83" s="3">
         <v>21200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>20900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>21400</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8004,8 +8206,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8111,8 +8316,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8218,8 +8426,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8325,8 +8536,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8432,115 +8646,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-60400</v>
+      </c>
+      <c r="E89" s="3">
         <v>30500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-22800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>38400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>48500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-24900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-85900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>103900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-49000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-50700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-115000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>87000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-27200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>28100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-37800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>5400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>84200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>88800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-77100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>124000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-112100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-33700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>7600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>175700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-4900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>81700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>119400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>24800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-16000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>51400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>150800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-12600</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8578,115 +8798,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1300</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-1700</v>
       </c>
       <c r="G91" s="3">
         <v>-1700</v>
       </c>
       <c r="H91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-6800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-6600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-7800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-8300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-4500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-8400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-8800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-12200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-14200</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8792,8 +9016,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8899,115 +9126,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>7200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>15100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>35300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-8500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-4100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-7800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-4300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-7500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>30100</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9045,8 +9278,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9074,8 +9308,8 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9152,8 +9386,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9259,8 +9496,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9366,8 +9606,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9473,325 +9716,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-16400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>15700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-44800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-49400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>12500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>6800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>16500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-79200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>44000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>56100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>32100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-15100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-41200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-22100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-34200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-14900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-32900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-53700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>112300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-66300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>36300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-172400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-71700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>12000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-45200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-162900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>28500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-22000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-92600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-12300</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>700</v>
+      </c>
+      <c r="E101" s="3">
         <v>3200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>6600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>3200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>6600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>3200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1300</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>1000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-6600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>4100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-2600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>12500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>2600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>600</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>4800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>3500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>4700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-3600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-10600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>10800</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-45300</v>
+      </c>
+      <c r="E102" s="3">
         <v>15900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-7800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-16200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>4700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-71800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>30400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-88800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>68800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-71300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>6300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-63500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-6800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>46400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>32500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>44500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>52700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-79400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-44600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-131800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>173100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-5800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>11900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>64300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-152900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>23500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>61400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>4100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FOSL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FOSL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="92">
   <si>
     <t>FOSL</t>
   </si>
@@ -656,484 +656,497 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="25" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45843</v>
+      </c>
+      <c r="E7" s="2">
         <v>45752</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45654</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45563</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45472</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45381</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45290</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45108</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45017</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44835</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44744</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44653</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44562</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44471</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44380</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44289</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44198</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44107</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44016</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43925</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43827</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43736</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43645</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43554</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43463</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43372</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43099</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42826</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>220400</v>
+      </c>
+      <c r="E8" s="3">
         <v>233300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>342300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>287800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>260000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>254900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>421300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>344100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>322000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>325000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>499100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>436300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>371200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>375900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>604200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>491800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>410900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>363000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>528100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>435500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>259000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>390700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>711600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>539500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>501400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>465300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>786900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>608800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>576600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>569200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>920800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>688700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>596800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>581800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>959200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>738000</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>93700</v>
+      </c>
+      <c r="E9" s="3">
         <v>90300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>150200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>145600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>123100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>121600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>222000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>183800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>162400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>159100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>263800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>216700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>179800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>191500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>301800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>232300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>189100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>180500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>268500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>205700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>118400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>250400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>403700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>260900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>236300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>217300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>370000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>282300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>267600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>281500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>472700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>368800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>295500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>292300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>470100</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>352900</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>126700</v>
+      </c>
+      <c r="E10" s="3">
         <v>143000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>192100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>142200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>136900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>133300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>199200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>160300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>159600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>166000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>235400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>219600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>191400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>184400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>302400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>259500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>221800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>182500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>259600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>229800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>140600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>140300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>307900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>278600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>265100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>248000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>416900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>326500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>309000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>287700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>448100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>319900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>301300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>289500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>489100</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>385100</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1172,8 +1185,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1192,11 +1206,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>19400</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1282,8 +1296,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1392,150 +1409,156 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E14" s="3">
         <v>15900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>36400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>5800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>17300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>10200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>15600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>15300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>7700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>12400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>6100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>6000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>7000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>12000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>17800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>9700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>14100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>28600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>12800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>25100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>9000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>11000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>4800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>6200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>21000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>23500</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>6400</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>5800</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>416900</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>26300</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>13300</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E15" s="3">
         <v>3400</v>
-      </c>
-      <c r="E15" s="3">
-        <v>3800</v>
       </c>
       <c r="F15" s="3">
         <v>3800</v>
       </c>
       <c r="G15" s="3">
+        <v>3800</v>
+      </c>
+      <c r="H15" s="3">
         <v>3900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4500</v>
-      </c>
-      <c r="I15" s="3">
-        <v>4600</v>
       </c>
       <c r="J15" s="3">
         <v>4600</v>
       </c>
       <c r="K15" s="3">
+        <v>4600</v>
+      </c>
+      <c r="L15" s="3">
         <v>4800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5100</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>8</v>
@@ -1549,8 +1572,8 @@
       <c r="Q15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R15" s="3">
-        <v>100</v>
+      <c r="R15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S15" s="3">
         <v>100</v>
@@ -1580,10 +1603,10 @@
         <v>100</v>
       </c>
       <c r="AB15" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC15" s="3">
         <v>400</v>
-      </c>
-      <c r="AC15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD15" s="3" t="s">
         <v>8</v>
@@ -1594,8 +1617,8 @@
       <c r="AF15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG15" s="3">
-        <v>0</v>
+      <c r="AG15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH15" s="3">
         <v>0</v>
@@ -1612,8 +1635,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1649,228 +1675,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>204600</v>
+      </c>
+      <c r="E17" s="3">
         <v>224100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>322200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>306400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>276700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>273900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>429700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>375200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>349600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>349900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>497900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>413800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>382100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>390100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>557000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>444000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>396600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>379800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>509800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>418000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>295800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>525100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>715600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>548600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>499700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>485200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>719600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>586200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>575600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>598100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>869600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>689200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1026600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>627100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>893000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>706800</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E18" s="3">
         <v>9200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>20100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-18600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-16800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-19000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-8400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-31100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-27600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-24900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>22500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-10900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-14200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>47200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>47800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>14300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-16800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>18300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>17500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-36800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-134400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-9100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-19900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>67300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>22600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-28900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>51200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-429800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-45300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>66200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>31200</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1909,558 +1942,574 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>3300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>8500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1500</v>
       </c>
-      <c r="H20" s="3">
-        <v>-2800</v>
-      </c>
       <c r="I20" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="J20" s="3">
         <v>1300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-7200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-15400</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-500</v>
       </c>
       <c r="S20" s="3">
         <v>-500</v>
       </c>
       <c r="T20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="U20" s="3">
         <v>1900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1600</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-7300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>5000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>25900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>5300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>3900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>5600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>7600</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E21" s="3">
         <v>9300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>15400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-11200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-11400</v>
       </c>
-      <c r="H21" s="3">
-        <v>-11800</v>
-      </c>
       <c r="I21" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="J21" s="3">
         <v>-5200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-29600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-15600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-17700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>26300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-6800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>38100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>54300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>21300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-6000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>29900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>27800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-25200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-129400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>14000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>3000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>16100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>20400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>93100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>35800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>15500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-14200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>72900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>22800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-406600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-18700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>95200</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>56300</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E22" s="3">
         <v>4500</v>
-      </c>
-      <c r="E22" s="3">
-        <v>4900</v>
       </c>
       <c r="F22" s="3">
         <v>4900</v>
       </c>
       <c r="G22" s="3">
+        <v>4900</v>
+      </c>
+      <c r="H22" s="3">
         <v>4100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>5100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>5700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>5000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>5800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>5100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>4300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>4000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>4800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>6400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>6500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>7300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>8500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>8000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>7900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>7500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>7000</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>7400</v>
       </c>
       <c r="AA22" s="3">
         <v>7400</v>
       </c>
       <c r="AB22" s="3">
+        <v>7400</v>
+      </c>
+      <c r="AC22" s="3">
         <v>8100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>10800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>9900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>11100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>10700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>11100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>12100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>11600</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>8400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>7500</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>7000</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-14500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-25200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-25800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-36600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-30400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-27800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-55200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-33500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-39600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>15500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-16900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-16700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>27100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>40900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-22200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>11400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>9500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-43800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-149100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-18000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>61800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>9900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-10600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-40900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>42400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-8700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-439400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-48000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>66300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>25800</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E24" s="3">
         <v>3400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-14000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-6100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-7200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>9200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>7300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>9000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>8100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>15200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-6800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-20800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-63700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>6900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>9600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>13900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-3400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>6600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>87000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-96300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-1200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>15500</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2569,228 +2618,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-17900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-11200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-31900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-38800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-24300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-28400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-60800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-26300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-41200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-18900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-21300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>19800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>31900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-24300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>16200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-23000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-85400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-6700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-24900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-6600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-11800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>47900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>5900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-7200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-47500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-44600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-5500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-343100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-46800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>50800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-17600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-7600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-32000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-38800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-24300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-28200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-61100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-26500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-41300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-19100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-21500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>19600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>31400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-24400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-4000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>16000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-22500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-85600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-25900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-7300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-12200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>47600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>5000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-7800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-48300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-46300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-5400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-344700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-48200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>49700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2899,8 +2957,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2973,8 +3034,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -2991,11 +3052,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-33600</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3009,8 +3070,11 @@
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3119,8 +3183,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3229,228 +3296,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-8500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1500</v>
       </c>
-      <c r="H32" s="3">
-        <v>2800</v>
-      </c>
       <c r="I32" s="3">
+        <v>3900</v>
+      </c>
+      <c r="J32" s="3">
         <v>-1300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>7200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>15400</v>
-      </c>
-      <c r="R32" s="3">
-        <v>500</v>
       </c>
       <c r="S32" s="3">
         <v>500</v>
       </c>
       <c r="T32" s="3">
+        <v>500</v>
+      </c>
+      <c r="U32" s="3">
         <v>-1900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1600</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>7300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-25900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-5300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-3900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-5600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-7600</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-17600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-7600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-32000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-38800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-24300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-28200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-61100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-26500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-41300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-19100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-21500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>19600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>31400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-24400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-4000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>16000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-22500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-85600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-25900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-7300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-12200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>47600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>5000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-7800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-48300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-79900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-5400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-344700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-48200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>49700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3559,233 +3635,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-17600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-7600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-32000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-38800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-24300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-28200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-61100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-26500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-41300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-19100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-21500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>19600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>31400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-24400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-4000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>16000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-22500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-85600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-25900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-7300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-12200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>47600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>5000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-7800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-48300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-79900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-5400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-344700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-48200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>49700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45843</v>
+      </c>
+      <c r="E38" s="2">
         <v>45752</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45654</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45563</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45472</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45381</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45290</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45108</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45017</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44835</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44744</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44653</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44562</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44471</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44380</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44289</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44198</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44107</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44016</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43925</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43827</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43736</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43645</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43554</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43463</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43372</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43099</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42826</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3824,8 +3909,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3864,118 +3950,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>109900</v>
+      </c>
+      <c r="E41" s="3">
         <v>78300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>123600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>106300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>104900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>112900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>117200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>116100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>132100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>127100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>198700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>162600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>167100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>162600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>250800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>181800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>252300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>246700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>316000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>323600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>277600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>245400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>200200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>147500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>226600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>271400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>403400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>236100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>241800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>229900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>231200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>166900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>319800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>320700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>297300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>236000</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3983,11 +4073,11 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>1600</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -3995,11 +4085,11 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>600</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -4084,448 +4174,463 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>122200</v>
+      </c>
+      <c r="E43" s="3">
         <v>124600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>185600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>173700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>133100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>134400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>268900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>194000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>162700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>168900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>206100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>215000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>176500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>201100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>255100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>251500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>187600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>175500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>229800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>189800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>130100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>153400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>289700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>247600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>204200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>199900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>328000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>261700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>204700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>234200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>367000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>310900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>240400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>245300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>375500</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>321300</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>178100</v>
+      </c>
+      <c r="E44" s="3">
         <v>182100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>178600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>226400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>202100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>224100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>252800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>326700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>323900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>336500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>376000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>452700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>437900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>385800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>346900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>398300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>352000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>322500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>295300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>359500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>375900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>439700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>452300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>570300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>460300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>384100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>377600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>521300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>497800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>530700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>573800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>683000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>618100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>571500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>542500</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>699600</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3">
         <v>24600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>19200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>164400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>185000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>183300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>187700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>169900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>155800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>157300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>202400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>149400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>134900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>98100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>128600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>117200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>126400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>124400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>133100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>149600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>129400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>125000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>161700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>118900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>125500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>126500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>142800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>132000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>132700</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>493600</v>
+      </c>
+      <c r="E46" s="3">
         <v>482500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>554500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>575900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>542400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>637300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>710700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>784900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>797600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>804500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>945300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1015300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>964800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>937200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1022800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>987500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>949200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>947100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>990500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1007800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>881700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>967100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1059500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1091700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1015500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>988500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1258600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1148500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1069300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1156400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1291000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1286300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1304800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1280300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1347300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>1389600</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4559,47 +4664,47 @@
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="3">
-        <v>300</v>
+      <c r="N47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O47" s="3">
         <v>300</v>
       </c>
       <c r="P47" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Q47" s="3">
         <v>400</v>
       </c>
       <c r="R47" s="3">
+        <v>400</v>
+      </c>
+      <c r="S47" s="3">
         <v>5400</v>
-      </c>
-      <c r="S47" s="3">
-        <v>6800</v>
       </c>
       <c r="T47" s="3">
         <v>6800</v>
       </c>
       <c r="U47" s="3">
+        <v>6800</v>
+      </c>
+      <c r="V47" s="3">
         <v>59100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>58000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>90400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>67000</v>
-      </c>
-      <c r="Y47" s="3">
-        <v>7000</v>
       </c>
       <c r="Z47" s="3">
         <v>7000</v>
       </c>
       <c r="AA47" s="3">
-        <v>7600</v>
+        <v>7000</v>
       </c>
       <c r="AB47" s="3">
         <v>7600</v>
@@ -4608,7 +4713,7 @@
         <v>7600</v>
       </c>
       <c r="AD47" s="3">
-        <v>1000</v>
+        <v>7600</v>
       </c>
       <c r="AE47" s="3">
         <v>1000</v>
@@ -4620,13 +4725,13 @@
         <v>1000</v>
       </c>
       <c r="AH47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AI47" s="3">
         <v>900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>7400</v>
-      </c>
-      <c r="AJ47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK47" s="3" t="s">
         <v>8</v>
@@ -4634,228 +4739,237 @@
       <c r="AL47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>160400</v>
+      </c>
+      <c r="E48" s="3">
         <v>157500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>163000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>180700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>187400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>196700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>208200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>223100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>220800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>225700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>236800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>233800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>249200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>251800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>267400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>280700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>297100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>316800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>340800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>363000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>387200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>407800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>439700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>447100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>470600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>484700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>183200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>190600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>200100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>208500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>219700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>243400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>255800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>260400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>273900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>290800</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>46000</v>
+        <v>900</v>
       </c>
       <c r="E49" s="3">
+        <v>900</v>
+      </c>
+      <c r="F49" s="3">
         <v>1000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>11400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>11900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>12400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>13000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>13600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>14300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>15000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>15800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>16500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>17800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>19300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>20800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>22400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>26900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>28000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>46400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>48100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>68300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>71300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>74300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>83900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>86700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>89500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>92500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>499800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>502400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>515800</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4964,8 +5078,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5074,118 +5191,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>8</v>
+      <c r="D52" s="3">
+        <v>22200</v>
       </c>
       <c r="E52" s="3">
+        <v>19000</v>
+      </c>
+      <c r="F52" s="3">
         <v>19400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>21400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>22000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>22600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>23800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>24200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>23200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>23500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>44100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>53100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>56100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>62300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>63900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>67400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>68600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>61900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>70400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>74300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>71300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>68200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>71700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>66800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>68100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>61100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>57600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>58100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>61600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>65900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>59900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>130100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>115500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>61100</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>63400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>61500</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5294,118 +5417,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>704500</v>
+      </c>
+      <c r="E54" s="3">
         <v>686000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>763600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>812400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>785700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>891000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>978000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1063200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1073400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1086000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1238100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1315000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1283400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1265300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1368700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1356000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1337400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1349100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1478500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1522300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1451300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1532600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1604700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1640600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1608200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1589900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1575200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1469500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1406200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1515700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1658400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1750400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1776000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>2101700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>2186900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>2257600</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5444,8 +5573,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5484,156 +5614,160 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>122900</v>
+      </c>
+      <c r="E57" s="3">
         <v>118200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>157600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>159000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>132500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>142900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>147200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>158000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>139800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>120100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>191100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>204000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>208700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>198500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>229900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>246300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>213500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>201200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>178200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>213100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>127900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>132700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>172200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>193000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>178500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>138300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>169600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>159400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>139500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>133700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>205000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>248800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>163500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>151200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>163600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>193600</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>47300</v>
+      </c>
+      <c r="E58" s="3">
         <v>45300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>39500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>42700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>42200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>40700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>44000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>44200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>45500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>46100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>400</v>
-      </c>
-      <c r="O58" s="3">
-        <v>600</v>
       </c>
       <c r="P58" s="3">
         <v>600</v>
@@ -5642,61 +5776,61 @@
         <v>600</v>
       </c>
       <c r="R58" s="3">
+        <v>600</v>
+      </c>
+      <c r="S58" s="3">
         <v>41200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>38400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>37900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>41600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>21400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>25200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>21100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>26200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>21900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>66400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>65900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>126400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>128000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>127700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>127100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>40200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>32700</v>
-      </c>
-      <c r="AJ58" s="3">
-        <v>26400</v>
       </c>
       <c r="AK58" s="3">
         <v>26400</v>
@@ -5704,448 +5838,463 @@
       <c r="AL58" s="3">
         <v>26400</v>
       </c>
+      <c r="AM58" s="3">
+        <v>26400</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>34900</v>
+        <v>41900</v>
       </c>
       <c r="E59" s="3">
+        <v>40300</v>
+      </c>
+      <c r="F59" s="3">
         <v>43700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>41100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>40300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>49000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>63600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>60000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>50600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>60800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>234400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>224300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>212000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>233500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>305200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>281900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>269900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>268100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>338800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>315400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>310600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>309400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>360800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>314300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>282700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>292400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>309800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>283800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>240300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>263100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>302000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>264500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>217800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>209100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>224600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>204200</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>269800</v>
+      </c>
+      <c r="E60" s="3">
         <v>262600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>326600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>317500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>279700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>295400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>342500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>348600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>321500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>305100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>425900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>428700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>421300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>432700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>535600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>569400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>521800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>507200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>558500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>549900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>463700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>463200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>559200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>529100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>527600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>496500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>605800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>571200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>507500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>523900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>509100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>553500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>414100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>386700</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>414600</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>424100</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>277100</v>
+      </c>
+      <c r="E61" s="3">
         <v>276900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>276300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>294100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>281900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>332000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>344600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>398100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>378100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>375400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>216100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>293600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>248900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>183900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>141400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>97400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>139700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>157200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>185900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>217900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>243900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>298500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>178800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>242100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>162000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>161100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>269800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>269100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>268400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>335500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>443900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>444300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>613600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>589700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>610000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>697400</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E62" s="3">
         <v>21000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>16700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>38200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>36400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>36300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>32800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>37200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>36200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>38600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>193100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>202400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>219200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>219300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>226400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>246300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>266600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>275800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>294100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>331000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>347100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>354500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>362900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>359500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>379000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>383000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>111000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>99600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>113500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>129700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>124400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>99600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>93500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>142900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>146900</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>151100</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6254,8 +6403,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6364,8 +6516,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6474,118 +6629,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>570600</v>
+      </c>
+      <c r="E66" s="3">
         <v>561600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>626800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>650500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>598600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>664400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>726300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>784500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>736500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>719700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>832200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>921900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>886200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>838200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>905500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>915000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>929600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>941300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1039400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1099500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1055300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1117100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1101700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1131400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1069000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1044200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>989700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>942700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>891200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>994200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1082200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1109100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1132900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1129800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1180700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1284900</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6624,8 +6785,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6734,8 +6896,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6844,8 +7009,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6954,8 +7122,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7064,118 +7235,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-104100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-101800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-84300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-76700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-44700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-5900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>18400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>46600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>107700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>134200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>175500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>184900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>179100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>198100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>229100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>209500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>178100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>179300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>203700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>207700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>191700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>214200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>299800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>306700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>332600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>339900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>381600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>332000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>327000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>334800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>409700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>489500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>494900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>839600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>887800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>838100</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7284,8 +7461,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7394,8 +7574,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7504,118 +7687,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>150300</v>
+      </c>
+      <c r="E76" s="3">
         <v>140600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>148700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>164400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>189600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>229100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>254200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>281100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>339500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>369100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>405900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>393000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>397300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>427200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>463200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>440900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>407900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>407800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>439100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>422800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>396100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>415400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>503100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>509300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>539200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>545700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>585500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>526800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>515000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>521400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>576100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>641300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>643000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>971900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1006200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>972700</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7724,233 +7913,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45843</v>
+      </c>
+      <c r="E80" s="2">
         <v>45752</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45654</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45563</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45472</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45381</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45290</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45108</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45017</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44835</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44744</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44653</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44562</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44471</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44380</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44289</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44198</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44107</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44016</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43925</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43827</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43736</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43645</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43554</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43463</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43372</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43099</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42826</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-17600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-7600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-32000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-38800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-24300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-28200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-61100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-26500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-41300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-19100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-21500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>19600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>31400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-24400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-4000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>16000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-22500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-85600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-25900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-7300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-12200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>47600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>5000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-7800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-48300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-79900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-5400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-344700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-48200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>49700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7989,118 +8187,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E83" s="3">
         <v>4300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5800</v>
-      </c>
-      <c r="P83" s="3">
-        <v>6200</v>
       </c>
       <c r="Q83" s="3">
         <v>6200</v>
       </c>
       <c r="R83" s="3">
+        <v>6200</v>
+      </c>
+      <c r="S83" s="3">
         <v>7000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>7500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>8900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>10000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>10300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>10700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>12200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>12900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>13500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>13900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>14400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>20400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>16100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>15100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>16000</v>
-      </c>
-      <c r="AG83" s="3">
-        <v>19400</v>
       </c>
       <c r="AH83" s="3">
         <v>19400</v>
       </c>
       <c r="AI83" s="3">
+        <v>19400</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>21200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>20900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>21400</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8209,8 +8411,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8319,8 +8524,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8429,8 +8637,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8539,8 +8750,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8649,118 +8863,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-60400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>30500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-22800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>38400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>48500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-24900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-85900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>103900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-49000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-50700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-115000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>87000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-27200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>28100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-37800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>5400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>84200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>88800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-77100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>124000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-112100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-33700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>7600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>175700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-4900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>81700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-4300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>119400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>24800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-16000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>51400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>150800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-12600</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8799,118 +9019,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1700</v>
       </c>
-      <c r="H91" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-6800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-6600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-7800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-8300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-4500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-8400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-8800</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-12200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-14200</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9019,8 +9243,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9129,118 +9356,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E94" s="3">
         <v>700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>7200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>15100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-7600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-4900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>35300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-8500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-4100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-7800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-4300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-7500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>30100</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9279,8 +9512,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9311,8 +9545,8 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9389,8 +9623,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9499,8 +9736,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9609,8 +9849,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9719,334 +9962,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E100" s="3">
         <v>10200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-16400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>15700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-44800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-49400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>12500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>6800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>16500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-79200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>44000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>56100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>32100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-15100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-41200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-22100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-34200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-14900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-32900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-53700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>112300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-66300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>36300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-6100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-172400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-71700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>12000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-45200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-162900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>28500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-22000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-92600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-12300</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>400</v>
+      </c>
+      <c r="E101" s="3">
         <v>700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>3200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>6600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>3200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>6600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>3200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1300</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>1000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-6600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>4100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-2600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>12500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>2600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>600</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>4800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>3500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>4700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-3600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-10600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>10800</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-45300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>15900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-7800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-16200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>4700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-71800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>30400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-88800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>68800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-71300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>6300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-63500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-6800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>46400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>32500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>44500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>52700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-79400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-44600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-131800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>173100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-5800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>11900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>64300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-152900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>23500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>61400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>4100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FOSL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FOSL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="92">
   <si>
     <t>FOSL</t>
   </si>
@@ -656,510 +656,523 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="26" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="27" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46025</v>
+      </c>
+      <c r="E7" s="2">
         <v>45934</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45843</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45752</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45654</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45563</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45472</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45381</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45290</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45108</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45017</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44835</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44744</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44653</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44562</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44471</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44380</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44289</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44198</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44107</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44016</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43925</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43827</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43736</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43645</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43554</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43463</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43372</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43099</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42917</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42826</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>280500</v>
+      </c>
+      <c r="E8" s="3">
         <v>270200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>220400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>233300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>342300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>287800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>260000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>254900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>421300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>344100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>322000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>325000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>499100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>436300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>371200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>375900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>604200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>491800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>410900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>363000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>528100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>435500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>259000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>390700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>711600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>539500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>501400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>465300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>786900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>608800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>576600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>569200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>920800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>688700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>596800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>581800</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>959200</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>738000</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>119500</v>
+      </c>
+      <c r="E9" s="3">
         <v>137800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>93700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>90300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>150200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>145600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>123100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>121600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>222000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>183800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>162400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>159100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>263800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>216700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>179800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>191500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>301800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>232300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>189100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>180500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>268500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>205700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>118400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>250400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>403700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>260900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>236300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>217300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>370000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>282300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>267600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>281500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>472700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>368800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>295500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>292300</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>470100</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>352900</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>161000</v>
+      </c>
+      <c r="E10" s="3">
         <v>132400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>126700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>143000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>192100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>142200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>136900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>133300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>199200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>160300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>159600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>166000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>235400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>219600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>191400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>184400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>302400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>259500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>221800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>182500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>259600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>229800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>140600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>140300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>307900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>278600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>265100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>248000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>416900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>326500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>309000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>287700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>448100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>319900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>301300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>289500</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>489100</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>385100</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1200,8 +1213,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1226,11 +1240,11 @@
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="3">
         <v>19400</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -1316,8 +1330,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1432,124 +1449,130 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E14" s="3">
         <v>9000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>7300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>15900</v>
       </c>
-      <c r="G14" s="3">
-        <v>36400</v>
-      </c>
       <c r="H14" s="3">
+        <v>36200</v>
+      </c>
+      <c r="I14" s="3">
         <v>5800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>17300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>10200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>15600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>15300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>7700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>12400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>3100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>6100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>6000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>7000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>12000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>17800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>9700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>14100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>28600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>12800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>25100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>9000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>11000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>4800</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>6200</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>21000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>23500</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>6400</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>5800</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>416900</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>26300</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>13300</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1557,37 +1580,37 @@
         <v>3300</v>
       </c>
       <c r="E15" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F15" s="3">
         <v>3000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3400</v>
-      </c>
-      <c r="G15" s="3">
-        <v>3800</v>
       </c>
       <c r="H15" s="3">
         <v>3800</v>
       </c>
       <c r="I15" s="3">
+        <v>3800</v>
+      </c>
+      <c r="J15" s="3">
         <v>3900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4500</v>
-      </c>
-      <c r="K15" s="3">
-        <v>4600</v>
       </c>
       <c r="L15" s="3">
         <v>4600</v>
       </c>
       <c r="M15" s="3">
+        <v>4600</v>
+      </c>
+      <c r="N15" s="3">
         <v>4800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>5100</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>8</v>
@@ -1601,8 +1624,8 @@
       <c r="S15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T15" s="3">
-        <v>100</v>
+      <c r="T15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U15" s="3">
         <v>100</v>
@@ -1632,10 +1655,10 @@
         <v>100</v>
       </c>
       <c r="AD15" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE15" s="3">
         <v>400</v>
-      </c>
-      <c r="AE15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF15" s="3" t="s">
         <v>8</v>
@@ -1646,8 +1669,8 @@
       <c r="AH15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI15" s="3">
-        <v>0</v>
+      <c r="AI15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ15" s="3">
         <v>0</v>
@@ -1664,8 +1687,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1703,240 +1729,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>268000</v>
+      </c>
+      <c r="E17" s="3">
         <v>284600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>204600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>224100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>322200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>306400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>276700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>273900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>429700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>375200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>349600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>349900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>497900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>413800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>382100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>390100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>557000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>444000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>396600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>379800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>509800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>418000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>295800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>525100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>715600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>548600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>499700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>485200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>719600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>586200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>575600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>598100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>869600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>689200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1026600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>627100</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>893000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>706800</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-14400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>15800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>9200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>20100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-18600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-16800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-19000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-31100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-27600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-24900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>22500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-10900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-14200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>47200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>47800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>14300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-16800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>18300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>17500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-36800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-134400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-9100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-19900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>67300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>22600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-28900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>51200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-429800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-45300</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>66200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>31200</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1977,588 +2010,604 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E20" s="3">
         <v>4500</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>3300</v>
       </c>
-      <c r="G20" s="3">
-        <v>8500</v>
-      </c>
       <c r="H20" s="3">
+        <v>8600</v>
+      </c>
+      <c r="I20" s="3">
         <v>-3600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-7200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-15400</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-500</v>
       </c>
       <c r="U20" s="3">
         <v>-500</v>
       </c>
       <c r="V20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="W20" s="3">
         <v>1900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1600</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-7300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>5000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>25900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>5300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>3900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>2000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>5600</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>7600</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-15600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>18700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>9300</v>
       </c>
-      <c r="G21" s="3">
-        <v>15400</v>
-      </c>
       <c r="H21" s="3">
+        <v>15200</v>
+      </c>
+      <c r="I21" s="3">
         <v>-11200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-11400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-10700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-5200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-29600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-15600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-17700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>26300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-6800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-6500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>38100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>54300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>21300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-6000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>29900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>27800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-25200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-129400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>14000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>3000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>16100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>20400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>93100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>35800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>15500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-14200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>72900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>22800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-406600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-18700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>95200</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>56300</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E22" s="3">
         <v>4200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4500</v>
-      </c>
-      <c r="G22" s="3">
-        <v>4900</v>
       </c>
       <c r="H22" s="3">
         <v>4900</v>
       </c>
       <c r="I22" s="3">
+        <v>4900</v>
+      </c>
+      <c r="J22" s="3">
         <v>4100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>5800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>5300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>5000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>5800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>5100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>4300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>4000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>4800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>6400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>6500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>7300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>8500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>8000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>7900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>7500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>7000</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>7400</v>
       </c>
       <c r="AC22" s="3">
         <v>7400</v>
       </c>
       <c r="AD22" s="3">
+        <v>7400</v>
+      </c>
+      <c r="AE22" s="3">
         <v>8100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>10800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>9900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>11100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>10700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>11100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>12100</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>11600</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>8400</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>7500</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>7000</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-32100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-14500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-25200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-25800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-36600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-30400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-27800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-55200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-33500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-39600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>15500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-16900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-16700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>27100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>40900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>7300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-22200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>11400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>9500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-43800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-149100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-18000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>61800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>9900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-10600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-40900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>42400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-8700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-439400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-48000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>66300</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>25800</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E24" s="3">
         <v>8000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>6200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-14000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-6100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-7200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>9200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>4700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>9000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>8100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>15200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-6800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-20800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-63700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>6900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>9600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>13900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-3400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>6600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>87000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-96300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-1200</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>15500</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>6500</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2673,240 +2722,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-40000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-17900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-11200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-31900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-38800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-24300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-28400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-60800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-26300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-41200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-18900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-21300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>19800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>31900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-24300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>16200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-23000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-85400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-6700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-24900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-6600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-11800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>47900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>5900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-7200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-47500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-44600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-5500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-343100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-46800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>50800</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-18600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-39900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-17600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-7600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-32000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-38800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-24300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-28200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-61100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-26500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-41300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-19100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-21500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>19600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>31400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-24400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-4000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>16000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-22500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-85600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-6900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-25900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-7300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-12200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>47600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>5000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-7800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-48300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-46300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-5400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-344700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-48200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>49700</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3021,8 +3079,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3101,8 +3162,8 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -3119,11 +3180,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-33600</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
@@ -3137,8 +3198,11 @@
       <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3253,8 +3317,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3369,240 +3436,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4500</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-3300</v>
       </c>
-      <c r="G32" s="3">
-        <v>-8500</v>
-      </c>
       <c r="H32" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="I32" s="3">
         <v>3600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>7200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>15400</v>
-      </c>
-      <c r="T32" s="3">
-        <v>500</v>
       </c>
       <c r="U32" s="3">
         <v>500</v>
       </c>
       <c r="V32" s="3">
+        <v>500</v>
+      </c>
+      <c r="W32" s="3">
         <v>-1900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1600</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>7300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-25900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-5300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-3900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-5600</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-7600</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-18600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-39900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-17600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-7600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-32000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-38800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-24300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-28200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-61100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-26500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-41300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-19100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-21500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>19600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>31400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-24400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-4000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>16000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-22500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-85600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-6900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-25900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-7300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-12200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>47600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>5000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-7800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-48300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-79900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-5400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-344700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-48200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>49700</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3717,245 +3793,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-18600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-39900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-17600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-7600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-32000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-38800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-24300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-28200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-61100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-26500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-41300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-19100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-21500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>19600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>31400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-24400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-4000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>16000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-22500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-85600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-6900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-25900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-7300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-12200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>47600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>5000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-7800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-48300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-79900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-5400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-344700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-48200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>49700</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46025</v>
+      </c>
+      <c r="E38" s="2">
         <v>45934</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45843</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45752</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45654</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45563</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45472</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45381</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45290</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45108</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45017</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44835</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44744</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44653</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44562</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44471</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44380</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44289</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44198</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44107</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44016</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43925</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43827</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43736</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43645</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43554</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43463</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43372</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43099</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42917</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42826</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3996,8 +4081,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4038,129 +4124,133 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>95800</v>
+      </c>
+      <c r="E41" s="3">
         <v>79200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>109900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>78300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>123600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>106300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>104900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>112900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>117200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>116100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>132100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>127100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>198700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>162600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>167100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>162600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>250800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>181800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>252300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>246700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>316000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>323600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>277600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>245400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>200200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>147500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>226600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>271400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>403400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>236100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>241800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>229900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>231200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>166900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>319800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>320700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>297300</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>236000</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -4169,11 +4259,11 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>1600</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -4181,11 +4271,11 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>600</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -4270,245 +4360,254 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>144600</v>
+      </c>
+      <c r="E43" s="3">
         <v>162500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>122200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>124600</v>
       </c>
-      <c r="G43" s="3">
-        <v>185600</v>
-      </c>
       <c r="H43" s="3">
+        <v>162200</v>
+      </c>
+      <c r="I43" s="3">
         <v>173700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>133100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>134400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>268900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>194000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>162700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>168900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>206100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>215000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>176500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>201100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>255100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>251500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>187600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>175500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>229800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>189800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>130100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>153400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>289700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>247600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>204200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>199900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>328000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>261700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>204700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>234200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>367000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>310900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>240400</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>245300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>375500</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>321300</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>151800</v>
+      </c>
+      <c r="E44" s="3">
         <v>166800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>178100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>182100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>178600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>226400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>202100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>224100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>252800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>326700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>323900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>336500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>376000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>452700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>437900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>385800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>346900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>398300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>352000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>322500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>295300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>359500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>375900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>439700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>452300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>570300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>460300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>384100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>377600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>521300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>497800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>530700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>573800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>683000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>618100</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>571500</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>542500</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>699600</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>29800</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>8</v>
@@ -4516,226 +4615,232 @@
       <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G45" s="3">
-        <v>24600</v>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H45" s="3">
+        <v>48100</v>
+      </c>
+      <c r="I45" s="3">
         <v>100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>19200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>164400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>185000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>183300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>187700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>169900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>155800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>157300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>202400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>149400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>134900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>98100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>128600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>117200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>126400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>124400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>133100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>149600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>129400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>125000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>161700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>118900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>125500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>126500</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>142800</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>132000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>132700</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>467800</v>
+      </c>
+      <c r="E46" s="3">
         <v>471100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>493600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>482500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>554500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>575900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>542400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>637300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>710700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>784900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>797600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>804500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>945300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1015300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>964800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>937200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1022800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>987500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>949200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>947100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>990500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1007800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>881700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>967100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1059500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1091700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1015500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>988500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1258600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1148500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1069300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1156400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1291000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1286300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1304800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>1280300</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>1347300</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>1389600</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4775,47 +4880,47 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>300</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>300</v>
       </c>
       <c r="R47" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="S47" s="3">
         <v>400</v>
       </c>
       <c r="T47" s="3">
+        <v>400</v>
+      </c>
+      <c r="U47" s="3">
         <v>5400</v>
-      </c>
-      <c r="U47" s="3">
-        <v>6800</v>
       </c>
       <c r="V47" s="3">
         <v>6800</v>
       </c>
       <c r="W47" s="3">
+        <v>6800</v>
+      </c>
+      <c r="X47" s="3">
         <v>59100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>58000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>90400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>67000</v>
-      </c>
-      <c r="AA47" s="3">
-        <v>7000</v>
       </c>
       <c r="AB47" s="3">
         <v>7000</v>
       </c>
       <c r="AC47" s="3">
-        <v>7600</v>
+        <v>7000</v>
       </c>
       <c r="AD47" s="3">
         <v>7600</v>
@@ -4824,7 +4929,7 @@
         <v>7600</v>
       </c>
       <c r="AF47" s="3">
-        <v>1000</v>
+        <v>7600</v>
       </c>
       <c r="AG47" s="3">
         <v>1000</v>
@@ -4836,13 +4941,13 @@
         <v>1000</v>
       </c>
       <c r="AJ47" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AK47" s="3">
         <v>900</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>7400</v>
-      </c>
-      <c r="AL47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM47" s="3" t="s">
         <v>8</v>
@@ -4850,240 +4955,249 @@
       <c r="AN47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>152400</v>
+      </c>
+      <c r="E48" s="3">
         <v>158400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>160400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>157500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>163000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>180700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>187400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>196700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>208200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>223100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>220800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>225700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>236800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>233800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>249200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>251800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>267400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>280700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>297100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>316800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>340800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>363000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>387200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>407800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>439700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>447100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>470600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>484700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>183200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>190600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>200100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>208500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>219700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>243400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>255800</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>260400</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>273900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>290800</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E49" s="3">
         <v>9800</v>
-      </c>
-      <c r="E49" s="3">
-        <v>900</v>
       </c>
       <c r="F49" s="3">
         <v>900</v>
       </c>
       <c r="G49" s="3">
+        <v>900</v>
+      </c>
+      <c r="H49" s="3">
         <v>1000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>11700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>11800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>11900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>12400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>13000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>13600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>14300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>15000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>15800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>16500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>17800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>19300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>20800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>22400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>26900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>28000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>46400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>48100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>68300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>71300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>74300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>83900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>86700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>89500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>92500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>499800</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>502400</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>515800</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5198,8 +5312,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5314,124 +5431,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E52" s="3">
         <v>18700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>22200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>19000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>19400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>21400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>22000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>22600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>23800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>24200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>23200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>23500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>44100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>53100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>56100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>62300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>63900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>67400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>68600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>61900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>70400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>74300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>71300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>68200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>71700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>66800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>68100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>61100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>57600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>58100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>61600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>65900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>59900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>130100</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>115500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>61100</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>63400</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>61500</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5546,124 +5669,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>689300</v>
+      </c>
+      <c r="E54" s="3">
         <v>701000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>704500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>686000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>763600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>812400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>785700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>891000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>978000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1063200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1073400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1086000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1238100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1315000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1283400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1265300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1368700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1356000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1337400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1349100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1478500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1522300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1451300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1532600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1604700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1640600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1608200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1589900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1575200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1469500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1406200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1515700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1658400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1750400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1776000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>2101700</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>2186900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>2257600</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5704,8 +5833,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5746,168 +5876,172 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>132500</v>
+      </c>
+      <c r="E57" s="3">
         <v>133800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>122900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>118200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>157600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>159000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>132500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>142900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>147200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>158000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>139800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>120100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>191100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>204000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>208700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>198500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>229900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>246300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>213500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>201200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>178200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>213100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>127900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>132700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>172200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>193000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>178500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>138300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>169600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>159400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>139500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>133700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>205000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>248800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>163500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>151200</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>163600</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>193600</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>38800</v>
+      </c>
+      <c r="E58" s="3">
         <v>43000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>47300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>45300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>39500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>42700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>42200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>40700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>44000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>44200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>45500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>46100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>400</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>600</v>
       </c>
       <c r="R58" s="3">
         <v>600</v>
@@ -5916,61 +6050,61 @@
         <v>600</v>
       </c>
       <c r="T58" s="3">
+        <v>600</v>
+      </c>
+      <c r="U58" s="3">
         <v>41200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>38400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>37900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>41600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>21400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>25200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>21100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>26200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>21900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>66400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>65900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>126400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>128000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>127700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>127100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>2100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>40200</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>32700</v>
-      </c>
-      <c r="AL58" s="3">
-        <v>26400</v>
       </c>
       <c r="AM58" s="3">
         <v>26400</v>
@@ -5978,472 +6112,487 @@
       <c r="AN58" s="3">
         <v>26400</v>
       </c>
+      <c r="AO58" s="3">
+        <v>26400</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>45800</v>
+      </c>
+      <c r="E59" s="3">
         <v>46900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>41900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>40300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>43700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>41100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>40300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>49000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>63600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>60000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>50600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>60800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>234400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>224300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>212000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>233500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>305200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>281900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>269900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>268100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>338800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>315400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>310600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>309400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>360800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>314300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>282700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>292400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>309800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>283800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>240300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>263100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>302000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>264500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>217800</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>209100</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>224600</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>204200</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>301800</v>
+      </c>
+      <c r="E60" s="3">
         <v>302800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>269800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>262600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>326600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>317500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>279700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>295400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>342500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>348600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>321500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>305100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>425900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>428700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>421300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>432700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>535600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>569400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>521800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>507200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>558500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>549900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>463700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>463200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>559200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>529100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>527600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>496500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>605800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>571200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>507500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>523900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>509100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>553500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>414100</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>386700</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>414600</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>424100</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>278300</v>
+      </c>
+      <c r="E61" s="3">
         <v>277700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>277100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>276900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>276300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>294100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>281900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>332000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>344600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>398100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>378100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>375400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>216100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>293600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>248900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>183900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>141400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>97400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>139700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>157200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>185900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>217900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>243900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>298500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>178800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>242100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>162000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>161100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>269800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>269100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>268400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>335500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>443900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>444300</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>613600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>589700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>610000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>697400</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E62" s="3">
         <v>23300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>22600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>21000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>16700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>38200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>36400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>36300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>32800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>37200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>36200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>38600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>193100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>202400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>219200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>219300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>226400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>246300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>266600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>275800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>294100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>331000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>347100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>354500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>362900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>359500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>379000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>383000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>111000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>99600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>113500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>129700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>124400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>99600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>93500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>142900</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>146900</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>151100</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6558,8 +6707,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6674,8 +6826,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6790,124 +6945,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>602500</v>
+      </c>
+      <c r="E66" s="3">
         <v>604900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>570600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>561600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>626800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>650500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>598600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>664400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>726300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>784500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>736500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>719700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>832200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>921900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>886200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>838200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>905500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>915000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>929600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>941300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1039400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1099500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1055300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1117100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1101700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1131400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1069000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1044200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>989700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>942700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>891200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>994200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1082200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1109100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1132900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1129800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1180700</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1284900</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6948,8 +7109,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7064,8 +7226,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7180,8 +7345,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7296,8 +7464,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7412,124 +7583,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-162600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-144000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-104100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-101800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-84300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-76700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-44700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-5900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>18400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>46600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>107700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>134200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>175500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>184900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>179100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>198100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>229100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>209500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>178100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>179300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>203700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>207700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>191700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>214200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>299800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>306700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>332600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>339900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>381600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>332000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>327000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>334800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>409700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>489500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>494900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>839600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>887800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>838100</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7644,8 +7821,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7760,8 +7940,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7876,124 +8059,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>102800</v>
+      </c>
+      <c r="E76" s="3">
         <v>112600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>150300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>140600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>148700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>164400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>189600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>229100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>254200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>281100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>339500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>369100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>405900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>393000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>397300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>427200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>463200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>440900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>407900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>407800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>439100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>422800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>396100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>415400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>503100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>509300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>539200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>545700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>585500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>526800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>515000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>521400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>576100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>641300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>643000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>971900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>1006200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>972700</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8108,245 +8297,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46025</v>
+      </c>
+      <c r="E80" s="2">
         <v>45934</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45843</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45752</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45654</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45563</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45472</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45381</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45290</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45108</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45017</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44835</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44744</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44653</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44562</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44471</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44380</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44289</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44198</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44107</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44016</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43925</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43827</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43736</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43645</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43554</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43463</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43372</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43099</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42917</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42826</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-18600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-39900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-17600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-7600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-32000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-38800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-24300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-28200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-61100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-26500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-41300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-19100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-21500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>19600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>31400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-24400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-4000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>16000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-22500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-85600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-6900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-25900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-7300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-12200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>47600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>5000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-7800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-48300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-79900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-5400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-344700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-48200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>49700</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>17400</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8387,124 +8585,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3600</v>
+        <v>3300</v>
       </c>
       <c r="E83" s="3">
         <v>3600</v>
       </c>
       <c r="F83" s="3">
+        <v>3600</v>
+      </c>
+      <c r="G83" s="3">
         <v>4300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5800</v>
-      </c>
-      <c r="R83" s="3">
-        <v>6200</v>
       </c>
       <c r="S83" s="3">
         <v>6200</v>
       </c>
       <c r="T83" s="3">
+        <v>6200</v>
+      </c>
+      <c r="U83" s="3">
         <v>7000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>7500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>8900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>10000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>10300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>10700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>12200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>12900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>13500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>13900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>14400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>20400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>16100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>15100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>16000</v>
-      </c>
-      <c r="AI83" s="3">
-        <v>19400</v>
       </c>
       <c r="AJ83" s="3">
         <v>19400</v>
       </c>
       <c r="AK83" s="3">
+        <v>19400</v>
+      </c>
+      <c r="AL83" s="3">
         <v>21200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>20900</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>21400</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8619,8 +8821,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8735,8 +8940,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8851,8 +9059,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8967,8 +9178,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9083,124 +9297,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-22200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>9400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-60400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>30500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-22800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>38400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>48500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-24900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-85900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>103900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-49000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-50700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-115000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>87000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-27200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>28100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-37800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>5400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>84200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>88800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-77100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>124000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-112100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-33700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>7600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>175700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-4900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>81700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-4300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>119400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>24800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-16000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>51400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>150800</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-12600</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9241,124 +9461,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-6800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-6600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-7800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-3800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-8300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-4500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-8400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-8800</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-12200</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-14200</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9473,8 +9697,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9589,124 +9816,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>200</v>
+      </c>
+      <c r="E94" s="3">
         <v>900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>20200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>7200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>15100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-7600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-4900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>35300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-5100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-3900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-8500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-4100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-7800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-4300</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-7500</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>30100</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9747,8 +9980,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9785,8 +10019,8 @@
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9863,8 +10097,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9979,8 +10216,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10095,8 +10335,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10211,352 +10454,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-10800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>10200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-16400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>15700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-44800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-49400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>12500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>6800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>16500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-79200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>44000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>56100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>32100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-15100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-41200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-22100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-34200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-14900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-32900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-53700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>112300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-66300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>36300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-6100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-172400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-71700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>12000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-45200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-162900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>28500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-22000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-92600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-12300</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E101" s="3">
         <v>1600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>3200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>6600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>6600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>3200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-3500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1300</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>1000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-6600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>4100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>12500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>2600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>600</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>4800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>3500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>4700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-3600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-10600</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>10800</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-27600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>32100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-45300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>15900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-7800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-16200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-71800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>30400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-88800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>68800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-71300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>6300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-63500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-6800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>46400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>32500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>44500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>52700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-79400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-44600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-131800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>173100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-5800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>11900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>64300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-152900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>23500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>61400</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>4100</v>
       </c>
     </row>
